--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -569,7 +569,7 @@
         <v>44970</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>45105</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45181</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>43627</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>44215</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>44651</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>44995</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45184</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>44980</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44977</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45252</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>43381</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44950</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44970</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45040</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45236</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>44361</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>44552</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>44958</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45176</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45180</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>43768</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>44550</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>44551</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44662</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>44966</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>44970</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>44984</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>43488</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>43549</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>43777</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44468</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>44636</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>44651</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44846</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44887</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44950</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>44956</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45009</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>45105</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45142</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45204</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>45209</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45257</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>45294</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43403</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43486</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>43635</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>43651</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43847</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43850</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>43860</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>43906</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43930</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>43931</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44218</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44551</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44560</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44595</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44607</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44788</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44823</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44845</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>44852</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>44894</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44911</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>44960</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45005</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45160</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>45163</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>45173</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>45173</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>45183</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45208</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>45212</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>45253</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>45310</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45310</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45335</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43336</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>43336</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>43343</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>43355</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>43367</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>43378</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>43385</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>43412</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>43416</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>43424</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>43434</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>43438</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>43439</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>43440</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>43446</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>43446</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>43446</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43447</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43447</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43450</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43450</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43451</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>43462</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>43475</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>43476</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43486</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>43488</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>43495</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>43496</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>43500</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>43517</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>43521</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>43522</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>43528</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>43529</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43536</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43539</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>43559</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>43606</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>43606</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>43612</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>43641</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>43642</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>43651</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>43656</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>43656</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>43668</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>43676</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>43686</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>43692</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>43692</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>43706</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>43707</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>43711</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>43733</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>43733</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>43734</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>43738</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>43740</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>43741</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>43746</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>43747</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>43756</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>43761</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>43770</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>43770</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>43774</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>43780</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>43780</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>43780</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>43795</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>43796</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43797</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43797</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43801</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43801</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43802</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>43809</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>43809</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>43812</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>43829</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43839</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43843</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43853</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43853</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43859</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>43859</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>43874</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>43875</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>43878</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>43880</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>43882</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>43893</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>43896</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>43900</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>43906</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>43913</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>43913</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>43930</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>43936</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>43938</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43957</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43958</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>43964</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43965</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43983</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43985</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43985</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43985</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43993</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44006</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>44007</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>44008</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>44013</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44021</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44022</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>44025</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44029</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44043</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44049</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44056</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44056</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44056</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44085</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>44088</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44097</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44106</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>44111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         <v>44116</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>44123</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44144</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>44150</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>44151</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>44154</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>44164</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>44165</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>44166</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>44172</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44172</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>44200</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>44208</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>44208</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44211</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44214</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>44215</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>44218</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>44231</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44237</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>44266</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>44266</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>44270</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>44272</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44281</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44285</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>44286</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>44286</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>44290</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44291</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>44308</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44309</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>44323</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>44333</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>44335</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44335</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>44337</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>44337</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>44337</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>44347</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>44357</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>44358</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>44358</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>44365</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44368</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>44371</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>44376</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44382</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>44389</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>44389</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>44417</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44418</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>44421</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44431</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44434</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>44438</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44439</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44439</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>44439</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>44440</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44441</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>44446</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44452</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44452</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>44452</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>44452</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>44453</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>44453</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44453</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>44459</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44463</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>44469</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44469</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44469</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44474</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44480</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>44480</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>44481</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44482</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44491</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>44491</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44496</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>44496</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>44497</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44504</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>44515</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>44516</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>44518</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>44529</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>44532</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>44543</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>44547</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>44548</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>44560</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>44571</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>44578</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>44579</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>44579</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44580</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>44581</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44581</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44581</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44588</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>44592</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44593</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44594</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>44594</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>44594</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44597</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44600</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44603</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44616</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44617</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44620</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44627</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44627</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44627</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44627</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44631</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44631</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44634</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44636</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44636</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44638</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>44641</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44644</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>44648</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>44648</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>44656</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>44670</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44672</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>44677</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>44677</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>44684</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44684</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44686</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44687</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44689</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44696</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44698</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44700</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44701</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>44701</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44701</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44704</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44704</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>44704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>44704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>44705</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44708</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>44708</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44713</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>44713</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>44715</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44722</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>44725</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44726</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>44728</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>44732</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>44734</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>44734</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44735</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44739</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>44739</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44742</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>44743</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>44743</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>44747</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>44748</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>44749</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27233,7 +27233,7 @@
         <v>44750</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44750</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>44755</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>44756</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>44756</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>44756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>44769</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>44769</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>44778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>44778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>44781</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>44781</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>44788</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>44790</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44792</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44804</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44804</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44811</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44819</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44819</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>44824</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44827</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44837</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44837</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44841</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44841</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44843</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44845</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>44846</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>44847</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>44853</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>44853</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>44853</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>44858</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>44858</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>44858</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>44859</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>44861</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44868</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>44871</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44874</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>44880</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>44880</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>44880</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>44881</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>44883</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>44886</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>44887</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>44887</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44887</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44888</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>44890</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>44892</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>44894</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>44894</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>44894</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>44894</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>44896</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>44896</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>44900</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>44900</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44901</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>44902</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44903</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44906</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44906</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44907</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44907</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44908</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44909</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44909</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44911</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>44916</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>44916</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>44917</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>44917</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>44917</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>44922</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>44924</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>44924</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>44928</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>44929</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32381,7 +32381,7 @@
         <v>44936</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>44937</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>44939</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>44942</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>44944</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>44945</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>44945</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44945</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44950</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>44950</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>44953</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44953</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44956</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44956</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>44956</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>44959</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44964</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44964</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>44964</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>44964</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44964</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>44964</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44964</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44964</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>44964</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44964</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44965</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44965</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44966</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44966</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44966</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44971</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>44971</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44972</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>44973</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44978</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44978</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44978</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>44979</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>44980</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>44980</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>44980</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>44981</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>44984</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>44986</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>44986</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>44986</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>44988</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44991</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>44991</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>44994</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>45005</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45005</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45005</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45005</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>45005</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45005</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45005</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>45005</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45006</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45009</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45009</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45013</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>45020</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45021</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45022</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45022</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45027</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45027</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45028</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45029</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45030</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>45030</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45033</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45040</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45040</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45040</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>45040</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45040</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45041</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45043</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>45046</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45046</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>45046</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         <v>45048</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45048</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45049</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45051</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45055</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45057</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45057</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38182,7 +38182,7 @@
         <v>45057</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>45058</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45058</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>45058</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>45061</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45061</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45062</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>45063</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38653,7 +38653,7 @@
         <v>45063</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45070</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45071</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45072</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45075</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45075</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>45079</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>45080</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45090</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39191,7 +39191,7 @@
         <v>45091</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45092</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45092</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45092</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39424,7 +39424,7 @@
         <v>45096</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>45096</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>45096</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45098</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>45099</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>45103</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45104</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45104</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>45105</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>45105</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40024,7 +40024,7 @@
         <v>45105</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40081,7 +40081,7 @@
         <v>45105</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45105</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>45105</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>45105</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>45106</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>45114</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45114</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45119</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>45121</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45128</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>45128</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45130</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45133</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>45135</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45135</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45135</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>45138</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41167,7 +41167,7 @@
         <v>45146</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45148</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>45153</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45161</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45161</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45161</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45162</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>45162</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>45163</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>45163</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>45163</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>45166</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>45166</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45166</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45167</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45168</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45170</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45170</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45173</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45173</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45173</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45174</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45174</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45174</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45176</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>45176</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>45180</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>45181</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>45181</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>45182</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45182</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45187</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>45188</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45189</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45189</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>45190</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>45190</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>45190</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45190</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45190</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45191</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45191</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>45194</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45197</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45198</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45201</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45203</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45203</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>45204</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>45204</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45204</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45209</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>45209</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45217</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>45217</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>45218</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45222</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45222</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45223</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45223</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>45224</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>45226</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45229</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45803,7 +45803,7 @@
         <v>45229</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>45230</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45922,7 +45922,7 @@
         <v>45232</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>45233</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46041,7 +46041,7 @@
         <v>45237</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>45238</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45239</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45239</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45239</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45239</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>45242</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46450,7 +46450,7 @@
         <v>45243</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45243</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46569,7 +46569,7 @@
         <v>45244</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45244</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46683,7 +46683,7 @@
         <v>45244</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>45245</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>45245</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>45245</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45246</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45246</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45246</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45247</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>45247</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47211,7 +47211,7 @@
         <v>45247</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>45247</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>45247</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47382,7 +47382,7 @@
         <v>45247</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>45251</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45252</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45252</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45252</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45253</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45253</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45253</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45257</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45257</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45257</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45258</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45258</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>45259</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>45259</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>45261</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45265</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45265</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45265</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45275</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>45275</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45275</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45275</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>45279</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>45279</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>45279</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48889,7 +48889,7 @@
         <v>45279</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45279</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45281</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45281</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>45281</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45281</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45282</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>45282</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>45282</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>45296</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49459,7 +49459,7 @@
         <v>45296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>45301</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>45301</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>45301</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>45307</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49737,14 +49737,14 @@
     <row r="792" ht="15" customHeight="1">
       <c r="A792" t="inlineStr">
         <is>
-          <t>A 1951-2024</t>
+          <t>A 2011-2024</t>
         </is>
       </c>
       <c r="B792" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         </is>
       </c>
       <c r="G792" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="H792" t="n">
         <v>0</v>
@@ -49794,14 +49794,14 @@
     <row r="793" ht="15" customHeight="1">
       <c r="A793" t="inlineStr">
         <is>
-          <t>A 2011-2024</t>
+          <t>A 1951-2024</t>
         </is>
       </c>
       <c r="B793" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         </is>
       </c>
       <c r="G793" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="H793" t="n">
         <v>0</v>
@@ -49858,7 +49858,7 @@
         <v>45310</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45312</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45314</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45316</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45320</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45330</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z799"/>
+  <dimension ref="A1:Z800"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44970</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>45105</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45181</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>43627</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>44215</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>44651</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>44995</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45184</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>44980</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44977</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45252</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>43381</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44950</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44970</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45040</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45236</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>44361</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>44552</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>44958</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45176</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45180</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>43768</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>44550</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>44551</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44662</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>44966</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>44970</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>44984</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>43488</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>43549</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>43777</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44468</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>44636</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>44651</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44846</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44887</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44950</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>44956</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45009</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>45105</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45142</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45204</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>45209</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45257</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>45294</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43403</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43486</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>43635</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>43651</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43847</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43850</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>43860</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>43906</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43930</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>43931</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44218</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44551</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44560</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44595</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44607</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44788</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44823</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44845</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>44852</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>44894</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44911</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>44960</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45005</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45160</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>45163</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>45173</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>45173</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>45183</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45208</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>45212</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>45253</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7879,14 +7879,14 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 2332-2024</t>
+          <t>A 2298-2024</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7899,10 +7899,10 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -7933,49 +7933,45 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="S82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0360/artfynd/A 2332-2024 artfynd.xlsx", "A 2332-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0360/artfynd/A 2298-2024 artfynd.xlsx", "A 2298-2024")</f>
         <v/>
       </c>
       <c r="T82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0360/kartor/A 2332-2024 karta.png", "A 2332-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0360/kartor/A 2298-2024 karta.png", "A 2298-2024")</f>
         <v/>
       </c>
       <c r="V82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0360/klagomål/A 2332-2024 FSC-klagomål.docx", "A 2332-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0360/klagomål/A 2298-2024 FSC-klagomål.docx", "A 2298-2024")</f>
         <v/>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0360/klagomålsmail/A 2332-2024 FSC-klagomål mail.docx", "A 2332-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0360/klagomålsmail/A 2298-2024 FSC-klagomål mail.docx", "A 2298-2024")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0360/tillsyn/A 2332-2024 tillsynsbegäran.docx", "A 2332-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0360/tillsyn/A 2298-2024 tillsynsbegäran.docx", "A 2298-2024")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0360/tillsynsmail/A 2332-2024 tillsynsbegäran mail.docx", "A 2332-2024")</f>
-        <v/>
-      </c>
-      <c r="Z82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0360/fåglar/A 2332-2024 prioriterade fågelarter.docx", "A 2332-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0360/tillsynsmail/A 2298-2024 tillsynsbegäran mail.docx", "A 2298-2024")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 2298-2024</t>
+          <t>A 2332-2024</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7988,10 +7984,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -8022,31 +8018,35 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="S83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0360/artfynd/A 2298-2024 artfynd.xlsx", "A 2298-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0360/artfynd/A 2332-2024 artfynd.xlsx", "A 2332-2024")</f>
         <v/>
       </c>
       <c r="T83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0360/kartor/A 2298-2024 karta.png", "A 2298-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0360/kartor/A 2332-2024 karta.png", "A 2332-2024")</f>
         <v/>
       </c>
       <c r="V83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0360/klagomål/A 2298-2024 FSC-klagomål.docx", "A 2298-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0360/klagomål/A 2332-2024 FSC-klagomål.docx", "A 2332-2024")</f>
         <v/>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0360/klagomålsmail/A 2298-2024 FSC-klagomål mail.docx", "A 2298-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0360/klagomålsmail/A 2332-2024 FSC-klagomål mail.docx", "A 2332-2024")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0360/tillsyn/A 2298-2024 tillsynsbegäran.docx", "A 2298-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0360/tillsyn/A 2332-2024 tillsynsbegäran.docx", "A 2332-2024")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0360/tillsynsmail/A 2298-2024 tillsynsbegäran mail.docx", "A 2298-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0360/tillsynsmail/A 2332-2024 tillsynsbegäran mail.docx", "A 2332-2024")</f>
+        <v/>
+      </c>
+      <c r="Z83">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0360/fåglar/A 2332-2024 prioriterade fågelarter.docx", "A 2332-2024")</f>
         <v/>
       </c>
     </row>
@@ -8060,7 +8060,7 @@
         <v>45335</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43336</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>43336</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>43343</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>43355</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>43367</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>43378</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>43385</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>43412</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>43416</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>43424</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>43434</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>43438</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>43439</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>43440</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>43446</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>43446</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>43446</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43447</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43447</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43450</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43450</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43451</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>43462</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>43475</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>43476</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43486</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>43488</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>43495</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>43496</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>43500</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>43517</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>43521</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>43522</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>43528</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>43529</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43536</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43539</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>43559</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>43606</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>43606</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>43612</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>43641</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>43642</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>43651</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>43656</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>43656</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>43668</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>43676</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>43686</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>43692</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>43692</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>43706</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>43707</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>43711</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>43733</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>43733</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>43734</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>43738</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>43740</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>43741</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>43746</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>43747</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>43756</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>43761</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>43770</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>43770</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>43774</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>43780</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>43780</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>43780</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>43795</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>43796</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43797</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43797</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43801</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43801</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43802</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>43809</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>43809</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>43812</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>43829</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43839</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43843</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43853</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43853</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43859</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>43859</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>43874</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>43875</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>43878</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>43880</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>43882</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>43893</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>43896</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>43900</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>43906</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>43913</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>43913</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>43930</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>43936</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>43938</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43957</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43958</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>43964</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43965</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43983</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43985</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43985</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43985</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43993</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44006</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>44007</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>44008</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>44013</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44021</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44022</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>44025</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44029</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44043</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44049</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44056</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44056</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44056</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44085</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>44088</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44097</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44106</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>44111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         <v>44116</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>44123</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44144</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>44150</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>44151</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>44154</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>44164</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>44165</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>44166</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>44172</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44172</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>44200</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>44208</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>44208</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44211</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44214</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>44215</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>44218</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>44231</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44237</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>44266</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>44266</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>44270</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>44272</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44281</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44285</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>44286</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>44286</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>44290</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44291</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>44308</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44309</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>44323</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>44333</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>44335</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44335</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>44337</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>44337</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>44337</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>44347</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>44357</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>44358</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>44358</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>44365</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44368</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>44371</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>44376</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44382</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>44389</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>44389</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>44417</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44418</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>44421</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44431</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44434</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>44438</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44439</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44439</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>44439</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>44440</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44441</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>44446</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44452</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44452</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>44452</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>44452</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>44453</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>44453</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44453</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>44459</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44463</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>44469</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44469</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44469</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44474</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44480</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>44480</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>44481</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44482</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44491</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>44491</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44496</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>44496</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>44497</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44504</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>44515</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>44516</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>44518</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>44529</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>44532</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>44543</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>44547</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>44548</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>44560</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>44571</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>44578</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>44579</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>44579</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44580</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>44581</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44581</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44581</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44588</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>44592</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44593</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44594</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>44594</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>44594</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44597</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44600</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44603</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44616</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44617</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44620</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44627</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44627</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44627</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44627</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44631</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44631</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44634</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44636</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44636</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44638</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>44641</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44644</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>44648</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>44648</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>44656</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>44670</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44672</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>44677</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>44677</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>44684</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44684</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44686</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44687</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44689</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44696</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44698</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44700</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44701</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>44701</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44701</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44704</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44704</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>44704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>44704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>44705</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44708</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>44708</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44713</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>44713</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>44715</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44722</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>44725</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44726</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>44728</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>44732</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>44734</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>44734</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44735</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44739</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>44739</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44742</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>44743</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>44743</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>44747</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>44748</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>44749</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27233,7 +27233,7 @@
         <v>44750</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44750</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>44755</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>44756</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>44756</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>44756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>44769</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>44769</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>44778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>44778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>44781</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>44781</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>44788</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>44790</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44792</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44804</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44804</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44811</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44819</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44819</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>44824</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44827</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44837</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44837</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44841</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44841</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44843</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44845</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>44846</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>44847</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>44853</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>44853</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>44853</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>44858</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>44858</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>44858</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>44859</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>44861</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44868</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>44871</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44874</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>44880</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>44880</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>44880</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>44881</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>44883</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>44886</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>44887</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>44887</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44887</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44888</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>44890</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>44892</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>44894</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>44894</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>44894</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>44894</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>44896</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>44896</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>44900</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>44900</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44901</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>44902</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44903</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44906</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44906</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44907</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44907</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44908</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44909</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44909</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44911</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>44916</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>44916</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>44917</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>44917</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>44917</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>44922</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>44924</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>44924</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>44928</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>44929</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32381,7 +32381,7 @@
         <v>44936</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>44937</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>44939</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>44942</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>44944</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>44945</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>44945</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44945</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44950</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>44950</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>44953</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44953</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44956</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44956</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>44956</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>44959</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44964</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44964</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>44964</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>44964</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44964</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>44964</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44964</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44964</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>44964</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44964</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44965</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44965</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44966</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44966</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44966</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44971</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>44971</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44972</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>44973</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44978</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44978</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44978</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>44979</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>44980</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>44980</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>44980</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>44981</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>44984</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>44986</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>44986</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>44986</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>44988</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44991</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>44991</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>44994</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>45005</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45005</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45005</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45005</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>45005</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45005</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45005</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>45005</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45006</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45009</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45009</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45013</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>45020</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45021</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45022</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45022</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45027</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45027</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45028</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45029</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45030</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>45030</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45033</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45040</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45040</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45040</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>45040</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45040</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45041</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45043</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>45046</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45046</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>45046</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         <v>45048</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45048</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45049</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45051</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45055</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45057</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45057</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38182,7 +38182,7 @@
         <v>45057</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>45058</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45058</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>45058</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>45061</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45061</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45062</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>45063</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38653,7 +38653,7 @@
         <v>45063</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45070</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45071</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45072</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45075</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45075</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>45079</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>45080</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45090</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39191,7 +39191,7 @@
         <v>45091</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45092</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45092</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45092</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39424,7 +39424,7 @@
         <v>45096</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>45096</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>45096</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45098</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>45099</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>45103</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45104</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45104</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>45105</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>45105</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40024,7 +40024,7 @@
         <v>45105</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40081,7 +40081,7 @@
         <v>45105</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45105</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>45105</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>45105</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>45106</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>45114</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45114</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45119</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>45121</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45128</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>45128</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45130</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45133</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>45135</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45135</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45135</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>45138</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41167,7 +41167,7 @@
         <v>45146</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45148</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>45153</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45161</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45161</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45161</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45162</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>45162</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>45163</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>45163</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>45163</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>45166</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>45166</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45166</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45167</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45168</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45170</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45170</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45173</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45173</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45173</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45174</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45174</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45174</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45176</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>45176</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>45180</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>45181</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>45181</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>45182</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45182</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45187</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>45188</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45189</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45189</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>45190</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>45190</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>45190</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45190</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45190</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45191</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45191</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>45194</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45197</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45198</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45201</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45203</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45203</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>45204</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>45204</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45204</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45209</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>45209</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45217</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>45217</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>45218</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45222</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45222</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45223</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45223</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>45224</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>45226</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45229</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45803,7 +45803,7 @@
         <v>45229</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>45230</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45922,7 +45922,7 @@
         <v>45232</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>45233</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46041,7 +46041,7 @@
         <v>45237</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>45238</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45239</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45239</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45239</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45239</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>45242</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46450,7 +46450,7 @@
         <v>45243</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45243</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46569,7 +46569,7 @@
         <v>45244</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45244</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46683,7 +46683,7 @@
         <v>45244</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>45245</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>45245</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>45245</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45246</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45246</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45246</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45247</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>45247</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47211,7 +47211,7 @@
         <v>45247</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>45247</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>45247</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47382,7 +47382,7 @@
         <v>45247</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>45251</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45252</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45252</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45252</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45253</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45253</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45253</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45257</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45257</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45257</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45258</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45258</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>45259</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>45259</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>45261</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45265</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45265</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45265</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45275</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>45275</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45275</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45275</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>45279</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>45279</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>45279</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48889,7 +48889,7 @@
         <v>45279</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45279</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45281</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45281</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>45281</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45281</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45282</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>45282</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>45282</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>45296</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49459,7 +49459,7 @@
         <v>45296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>45301</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>45301</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>45301</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>45307</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49744,7 +49744,7 @@
         <v>45308</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49801,7 +49801,7 @@
         <v>45308</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45310</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45312</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45314</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45316</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45320</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
       </c>
       <c r="R798" s="2" t="inlineStr"/>
     </row>
-    <row r="799">
+    <row r="799" ht="15" customHeight="1">
       <c r="A799" t="inlineStr">
         <is>
           <t>A 5126-2024</t>
@@ -50143,7 +50143,7 @@
         <v>45330</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50189,6 +50189,63 @@
         <v>0</v>
       </c>
       <c r="R799" s="2" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>A 6395-2024</t>
+        </is>
+      </c>
+      <c r="B800" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C800" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>TIERP</t>
+        </is>
+      </c>
+      <c r="G800" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H800" t="n">
+        <v>0</v>
+      </c>
+      <c r="I800" t="n">
+        <v>0</v>
+      </c>
+      <c r="J800" t="n">
+        <v>0</v>
+      </c>
+      <c r="K800" t="n">
+        <v>0</v>
+      </c>
+      <c r="L800" t="n">
+        <v>0</v>
+      </c>
+      <c r="M800" t="n">
+        <v>0</v>
+      </c>
+      <c r="N800" t="n">
+        <v>0</v>
+      </c>
+      <c r="O800" t="n">
+        <v>0</v>
+      </c>
+      <c r="P800" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q800" t="n">
+        <v>0</v>
+      </c>
+      <c r="R800" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z800"/>
+  <dimension ref="A1:Z801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44970</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>45105</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45181</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>43627</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>44215</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>44651</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>44995</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45184</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>44980</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44977</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45252</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>43381</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44950</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44970</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45040</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45236</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>44361</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>44552</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>44958</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45176</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45180</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>43768</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>44550</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>44551</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44662</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>44966</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>44970</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>44984</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>43488</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>43549</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>43777</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44468</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>44636</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>44651</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44846</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44887</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44950</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>44956</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45009</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>45105</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45142</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45204</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>45209</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45257</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>45294</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43403</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43486</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>43635</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>43651</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43847</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43850</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>43860</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>43906</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43930</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>43931</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44218</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44551</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44560</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44595</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44607</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44788</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44823</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44845</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>44852</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>44894</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44911</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>44960</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45005</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45160</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>45163</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>45173</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>45173</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>45183</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45208</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>45212</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>45253</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>45310</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>45310</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45335</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43336</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>43336</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>43343</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>43355</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>43367</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>43378</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>43385</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>43412</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>43416</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>43424</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>43434</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>43438</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>43439</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>43440</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>43446</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>43446</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>43446</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43447</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43447</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43450</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43450</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43451</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>43462</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>43475</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>43476</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43486</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>43488</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>43495</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>43496</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>43500</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>43517</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>43521</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>43522</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>43528</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>43529</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43536</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43539</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>43559</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>43606</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>43606</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>43612</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>43641</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>43642</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>43651</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>43656</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>43656</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>43668</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>43676</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>43686</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>43692</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>43692</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>43706</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>43707</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>43711</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>43733</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>43733</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>43734</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>43738</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>43740</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>43741</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>43746</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>43747</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>43756</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>43761</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>43770</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>43770</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>43774</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>43780</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>43780</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>43780</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>43795</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>43796</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43797</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43797</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43801</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43801</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43802</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>43809</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>43809</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>43812</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>43829</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43839</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43843</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43853</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43853</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43859</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>43859</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>43874</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>43875</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>43878</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>43880</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>43882</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>43893</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>43896</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>43900</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>43906</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>43913</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>43913</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>43930</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>43936</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>43938</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43957</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43958</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>43964</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43965</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43983</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43985</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43985</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43985</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43993</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44006</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>44007</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>44008</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>44013</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44021</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44022</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>44025</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44029</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44043</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44049</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44056</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44056</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44056</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44085</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>44088</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44097</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44106</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>44111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         <v>44116</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>44123</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44144</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>44150</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>44151</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>44154</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>44164</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>44165</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>44166</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>44172</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44172</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>44200</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>44208</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>44208</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44211</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44214</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>44215</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>44218</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>44231</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44237</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>44266</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>44266</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>44270</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>44272</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44281</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44285</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>44286</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>44286</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>44290</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44291</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>44308</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44309</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>44323</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>44333</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>44335</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44335</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>44337</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>44337</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>44337</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>44347</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>44357</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>44358</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>44358</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>44365</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44368</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>44371</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>44376</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44382</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>44389</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>44389</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>44417</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44418</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>44421</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44431</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44434</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>44438</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44439</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44439</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>44439</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>44440</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44441</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>44446</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44452</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44452</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>44452</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>44452</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>44453</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>44453</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44453</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>44459</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44463</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>44469</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44469</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44469</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44474</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44480</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>44480</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>44481</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44482</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44491</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>44491</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44496</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>44496</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>44497</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44504</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>44515</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>44516</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>44518</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>44529</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>44532</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>44543</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>44547</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>44548</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>44560</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>44571</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>44578</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>44579</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>44579</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44580</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>44581</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44581</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44581</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44588</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>44592</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44593</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44594</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>44594</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>44594</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44597</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44600</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44603</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44616</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44617</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44620</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44627</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44627</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44627</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44627</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44631</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44631</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44634</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44636</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44636</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44638</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>44641</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44644</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>44648</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>44648</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>44656</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>44670</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44672</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>44677</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>44677</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>44684</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44684</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44686</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44687</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44689</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44696</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44698</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44700</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44701</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>44701</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44701</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44704</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44704</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>44704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>44704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>44705</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44708</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>44708</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44713</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>44713</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>44715</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44722</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>44725</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44726</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>44728</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>44732</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>44734</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>44734</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44735</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44739</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>44739</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44742</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>44743</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>44743</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>44747</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>44748</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>44749</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27233,7 +27233,7 @@
         <v>44750</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44750</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>44755</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>44756</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>44756</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>44756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>44769</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>44769</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>44778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>44778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>44781</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>44781</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>44788</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>44790</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44792</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44804</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44804</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44811</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44819</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44819</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>44824</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44827</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44837</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44837</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44841</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44841</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44843</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44845</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>44846</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>44847</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>44853</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>44853</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>44853</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>44858</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>44858</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>44858</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>44859</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>44861</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44868</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>44871</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44874</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>44880</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>44880</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>44880</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>44881</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>44883</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>44886</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>44887</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>44887</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44887</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44888</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>44890</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>44892</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>44894</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>44894</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>44894</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>44894</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>44896</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>44896</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>44900</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>44900</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44901</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>44902</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44903</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44906</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44906</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44907</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44907</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44908</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44909</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44909</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44911</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>44916</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>44916</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>44917</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>44917</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>44917</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>44922</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>44924</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>44924</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>44928</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>44929</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32381,7 +32381,7 @@
         <v>44936</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>44937</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>44939</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>44942</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>44944</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>44945</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>44945</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44945</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44950</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>44950</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>44953</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44953</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44956</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44956</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>44956</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>44959</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44964</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44964</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>44964</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>44964</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44964</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>44964</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44964</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44964</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>44964</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44964</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44965</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44965</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44966</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44966</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44966</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44971</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>44971</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44972</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>44973</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44978</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44978</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44978</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>44979</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>44980</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>44980</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>44980</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>44981</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>44984</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>44986</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>44986</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>44986</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>44988</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44991</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>44991</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>44994</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>45005</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45005</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45005</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45005</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>45005</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45005</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45005</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>45005</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45006</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45009</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45009</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45013</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>45020</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45021</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45022</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45022</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45027</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45027</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45028</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45029</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45030</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>45030</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45033</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45040</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45040</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45040</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>45040</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45040</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45041</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45043</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>45046</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45046</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>45046</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         <v>45048</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45048</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45049</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45051</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45055</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45057</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45057</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38182,7 +38182,7 @@
         <v>45057</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>45058</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45058</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>45058</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>45061</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45061</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45062</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>45063</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38653,7 +38653,7 @@
         <v>45063</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45070</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45071</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45072</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45075</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45075</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>45079</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>45080</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45090</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39191,7 +39191,7 @@
         <v>45091</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45092</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45092</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45092</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39424,7 +39424,7 @@
         <v>45096</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>45096</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>45096</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45098</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>45099</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>45103</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45104</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45104</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>45105</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>45105</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40024,7 +40024,7 @@
         <v>45105</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40081,7 +40081,7 @@
         <v>45105</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45105</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>45105</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>45105</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>45106</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>45114</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45114</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45119</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>45121</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45128</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>45128</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45130</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45133</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>45135</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45135</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45135</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>45138</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41167,7 +41167,7 @@
         <v>45146</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45148</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>45153</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45161</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45161</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45161</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45162</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>45162</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>45163</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>45163</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>45163</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>45166</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>45166</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45166</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45167</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45168</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45170</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45170</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45173</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45173</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45173</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45174</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45174</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45174</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45176</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>45176</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>45180</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>45181</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>45181</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>45182</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45182</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45187</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>45188</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45189</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45189</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>45190</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>45190</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>45190</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45190</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45190</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45191</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45191</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>45194</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45197</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45198</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45201</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45203</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45203</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>45204</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>45204</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45204</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45209</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>45209</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45217</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>45217</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>45218</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45222</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45222</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45223</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45223</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>45224</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>45226</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45229</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45803,7 +45803,7 @@
         <v>45229</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>45230</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45922,7 +45922,7 @@
         <v>45232</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>45233</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46041,7 +46041,7 @@
         <v>45237</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>45238</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45239</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45239</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45239</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45239</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>45242</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46450,7 +46450,7 @@
         <v>45243</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45243</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46569,7 +46569,7 @@
         <v>45244</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45244</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46683,7 +46683,7 @@
         <v>45244</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>45245</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>45245</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>45245</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45246</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45246</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45246</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45247</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>45247</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47211,7 +47211,7 @@
         <v>45247</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>45247</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>45247</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47382,7 +47382,7 @@
         <v>45247</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>45251</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45252</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45252</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45252</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45253</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45253</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45253</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45257</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45257</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45257</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45258</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45258</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>45259</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>45259</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>45261</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45265</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45265</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45265</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45275</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>45275</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45275</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45275</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>45279</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>45279</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>45279</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48889,7 +48889,7 @@
         <v>45279</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45279</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45281</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45281</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>45281</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45281</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45282</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>45282</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>45282</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>45296</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49459,7 +49459,7 @@
         <v>45296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>45301</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>45301</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>45301</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>45307</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49744,7 +49744,7 @@
         <v>45308</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49801,7 +49801,7 @@
         <v>45308</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45310</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45312</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45314</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45316</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45320</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45330</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50190,7 +50190,7 @@
       </c>
       <c r="R799" s="2" t="inlineStr"/>
     </row>
-    <row r="800">
+    <row r="800" ht="15" customHeight="1">
       <c r="A800" t="inlineStr">
         <is>
           <t>A 6395-2024</t>
@@ -50200,7 +50200,7 @@
         <v>45338</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50246,6 +50246,63 @@
         <v>0</v>
       </c>
       <c r="R800" s="2" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>A 6385-2024</t>
+        </is>
+      </c>
+      <c r="B801" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C801" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>TIERP</t>
+        </is>
+      </c>
+      <c r="G801" t="n">
+        <v>2</v>
+      </c>
+      <c r="H801" t="n">
+        <v>0</v>
+      </c>
+      <c r="I801" t="n">
+        <v>0</v>
+      </c>
+      <c r="J801" t="n">
+        <v>0</v>
+      </c>
+      <c r="K801" t="n">
+        <v>0</v>
+      </c>
+      <c r="L801" t="n">
+        <v>0</v>
+      </c>
+      <c r="M801" t="n">
+        <v>0</v>
+      </c>
+      <c r="N801" t="n">
+        <v>0</v>
+      </c>
+      <c r="O801" t="n">
+        <v>0</v>
+      </c>
+      <c r="P801" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q801" t="n">
+        <v>0</v>
+      </c>
+      <c r="R801" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z801"/>
+  <dimension ref="A1:Z803"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44970</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>45105</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45181</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>43627</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>44215</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>44651</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>44995</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45184</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>44980</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44977</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45252</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>43381</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44950</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44970</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45040</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45236</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>44361</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>44552</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>44958</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45176</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45180</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>43768</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>44550</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>44551</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44662</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>44966</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>44970</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>44984</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>43488</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>43549</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>43777</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44468</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>44636</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>44651</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44846</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44887</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44950</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>44956</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45009</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>45105</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45142</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45204</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>45209</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45257</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>45294</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43403</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43486</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>43635</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>43651</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43847</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43850</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>43860</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>43906</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43930</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>43931</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44218</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44551</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44560</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44595</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44607</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44788</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44823</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44845</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>44852</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>44894</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44911</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>44960</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45005</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45160</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>45163</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>45173</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>45173</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>45183</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45208</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>45212</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>45253</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>45310</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>45310</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45335</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43336</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>43336</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>43343</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>43355</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>43367</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>43378</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>43385</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>43412</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>43416</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>43424</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>43434</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>43438</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>43439</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>43440</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>43446</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>43446</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>43446</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43447</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43447</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43450</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43450</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43451</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>43462</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>43475</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>43476</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43486</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>43488</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>43495</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>43496</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>43500</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>43517</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>43521</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>43522</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>43528</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>43529</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43536</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43539</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>43559</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>43606</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>43606</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>43612</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>43641</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>43642</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>43651</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>43656</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>43656</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>43668</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>43676</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>43686</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>43692</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>43692</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>43706</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>43707</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>43711</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>43733</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>43733</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>43734</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>43738</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>43740</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>43741</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>43746</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>43747</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>43756</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>43761</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>43770</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>43770</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>43774</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>43780</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>43780</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>43780</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>43795</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>43796</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43797</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43797</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43801</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43801</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43802</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>43809</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>43809</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>43812</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>43829</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43839</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43843</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43853</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43853</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43859</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>43859</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>43874</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>43875</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>43878</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>43880</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>43882</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>43893</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>43896</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>43900</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>43906</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>43913</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>43913</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>43930</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>43936</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>43938</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43957</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43958</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>43964</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43965</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43983</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43985</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43985</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43985</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43993</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44006</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>44007</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>44008</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>44013</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44021</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44022</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>44025</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44029</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44043</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44049</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44056</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44056</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44056</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44085</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>44088</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44097</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44106</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>44111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         <v>44116</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>44123</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44144</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>44150</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>44151</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>44154</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>44164</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>44165</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>44166</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>44172</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44172</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>44200</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>44208</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>44208</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44211</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44214</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>44215</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>44218</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>44231</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44237</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>44266</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>44266</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>44270</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>44272</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44281</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44285</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>44286</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>44286</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>44290</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44291</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>44308</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44309</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>44323</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>44333</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>44335</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44335</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>44337</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>44337</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>44337</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>44347</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>44357</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>44358</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>44358</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>44365</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44368</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>44371</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>44376</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44382</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>44389</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>44389</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>44417</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44418</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>44421</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44431</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44434</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>44438</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44439</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44439</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>44439</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>44440</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44441</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>44446</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44452</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44452</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>44452</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>44452</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>44453</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>44453</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44453</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>44459</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44463</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>44469</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44469</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44469</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44474</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44480</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>44480</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>44481</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44482</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44491</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>44491</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44496</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>44496</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>44497</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44504</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>44515</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>44516</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>44518</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>44529</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>44532</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>44543</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>44547</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>44548</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>44560</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>44571</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>44578</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>44579</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>44579</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44580</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>44581</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44581</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44581</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44588</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>44592</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44593</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44594</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>44594</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>44594</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44597</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44600</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44603</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44616</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44617</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44620</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44627</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44627</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44627</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44627</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44631</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44631</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44634</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44636</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44636</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44638</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>44641</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44644</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>44648</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>44648</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>44656</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>44670</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44672</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>44677</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>44677</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>44684</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44684</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44686</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44687</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44689</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44696</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44698</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44700</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44701</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>44701</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44701</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44704</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44704</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>44704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>44704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>44705</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44708</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>44708</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44713</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>44713</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>44715</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44722</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>44725</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44726</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>44728</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>44732</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>44734</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>44734</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44735</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44739</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>44739</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44742</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>44743</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>44743</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>44747</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>44748</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>44749</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27233,7 +27233,7 @@
         <v>44750</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44750</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>44755</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>44756</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>44756</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>44756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>44769</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>44769</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>44778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>44778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>44781</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>44781</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>44788</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>44790</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44792</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44804</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44804</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44811</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44819</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44819</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>44824</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44827</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44837</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44837</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44841</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44841</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44843</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44845</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>44846</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>44847</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>44853</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>44853</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>44853</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>44858</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>44858</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>44858</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>44859</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>44861</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44868</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>44871</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44874</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>44880</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>44880</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>44880</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>44881</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>44883</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>44886</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>44887</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>44887</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44887</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44888</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>44890</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>44892</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>44894</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>44894</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>44894</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>44894</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>44896</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>44896</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>44900</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>44900</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44901</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>44902</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44903</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44906</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44906</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44907</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44907</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44908</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44909</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44909</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44911</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>44916</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>44916</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>44917</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>44917</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>44917</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>44922</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>44924</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>44924</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>44928</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>44929</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32381,7 +32381,7 @@
         <v>44936</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>44937</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>44939</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>44942</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>44944</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>44945</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>44945</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44945</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44950</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>44950</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>44953</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44953</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44956</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44956</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>44956</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>44959</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44964</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44964</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>44964</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>44964</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44964</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>44964</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44964</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44964</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>44964</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44964</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44965</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44965</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44966</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44966</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44966</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44971</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>44971</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44972</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>44973</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44978</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44978</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44978</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>44979</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>44980</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>44980</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>44980</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>44981</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>44984</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>44986</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>44986</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>44986</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>44988</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44991</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>44991</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>44994</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>45005</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45005</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45005</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45005</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>45005</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45005</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45005</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>45005</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45006</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45009</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45009</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45013</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>45020</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45021</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45022</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45022</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45027</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45027</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45028</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45029</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45030</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>45030</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45033</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45040</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45040</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45040</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>45040</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45040</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45041</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45043</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>45046</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45046</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>45046</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         <v>45048</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45048</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45049</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45051</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45055</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45057</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45057</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38182,7 +38182,7 @@
         <v>45057</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>45058</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45058</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>45058</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>45061</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45061</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45062</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>45063</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38653,7 +38653,7 @@
         <v>45063</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45070</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45071</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45072</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45075</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45075</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>45079</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>45080</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45090</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39191,7 +39191,7 @@
         <v>45091</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45092</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45092</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45092</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39424,7 +39424,7 @@
         <v>45096</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>45096</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>45096</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45098</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>45099</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>45103</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45104</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45104</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>45105</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>45105</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40024,7 +40024,7 @@
         <v>45105</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40081,7 +40081,7 @@
         <v>45105</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45105</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>45105</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>45105</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>45106</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>45114</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45114</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45119</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>45121</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45128</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>45128</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45130</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45133</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>45135</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45135</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45135</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>45138</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41167,7 +41167,7 @@
         <v>45146</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45148</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>45153</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45161</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45161</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45161</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45162</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>45162</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>45163</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>45163</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>45163</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>45166</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>45166</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45166</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45167</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45168</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45170</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45170</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45173</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45173</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45173</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45174</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45174</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45174</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45176</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>45176</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>45180</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>45181</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>45181</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>45182</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45182</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45187</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>45188</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45189</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45189</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>45190</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>45190</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>45190</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45190</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45190</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45191</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45191</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>45194</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45197</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45198</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45201</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45203</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45203</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>45204</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>45204</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45204</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45209</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>45209</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45217</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>45217</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>45218</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45222</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45222</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45223</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45223</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>45224</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>45226</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45229</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45803,7 +45803,7 @@
         <v>45229</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>45230</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45922,7 +45922,7 @@
         <v>45232</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>45233</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46041,7 +46041,7 @@
         <v>45237</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>45238</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45239</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45239</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45239</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45239</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>45242</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46450,7 +46450,7 @@
         <v>45243</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45243</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46569,7 +46569,7 @@
         <v>45244</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45244</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46683,7 +46683,7 @@
         <v>45244</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>45245</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>45245</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>45245</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45246</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45246</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45246</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45247</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>45247</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47211,7 +47211,7 @@
         <v>45247</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>45247</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>45247</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47382,7 +47382,7 @@
         <v>45247</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>45251</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45252</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45252</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45252</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45253</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45253</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45253</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45257</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45257</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45257</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45258</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45258</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>45259</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>45259</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>45261</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45265</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45265</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45265</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45275</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>45275</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45275</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45275</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>45279</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>45279</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>45279</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48889,7 +48889,7 @@
         <v>45279</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45279</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45281</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45281</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>45281</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45281</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45282</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>45282</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>45282</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>45296</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49459,7 +49459,7 @@
         <v>45296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>45301</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>45301</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>45301</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>45307</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49744,7 +49744,7 @@
         <v>45308</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49801,7 +49801,7 @@
         <v>45308</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45310</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45312</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45314</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45316</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45320</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45330</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>45338</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
       </c>
       <c r="R800" s="2" t="inlineStr"/>
     </row>
-    <row r="801">
+    <row r="801" ht="15" customHeight="1">
       <c r="A801" t="inlineStr">
         <is>
           <t>A 6385-2024</t>
@@ -50257,7 +50257,7 @@
         <v>45338</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50303,6 +50303,120 @@
         <v>0</v>
       </c>
       <c r="R801" s="2" t="inlineStr"/>
+    </row>
+    <row r="802" ht="15" customHeight="1">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>A 7048-2024</t>
+        </is>
+      </c>
+      <c r="B802" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C802" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>TIERP</t>
+        </is>
+      </c>
+      <c r="G802" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H802" t="n">
+        <v>0</v>
+      </c>
+      <c r="I802" t="n">
+        <v>0</v>
+      </c>
+      <c r="J802" t="n">
+        <v>0</v>
+      </c>
+      <c r="K802" t="n">
+        <v>0</v>
+      </c>
+      <c r="L802" t="n">
+        <v>0</v>
+      </c>
+      <c r="M802" t="n">
+        <v>0</v>
+      </c>
+      <c r="N802" t="n">
+        <v>0</v>
+      </c>
+      <c r="O802" t="n">
+        <v>0</v>
+      </c>
+      <c r="P802" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q802" t="n">
+        <v>0</v>
+      </c>
+      <c r="R802" s="2" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>A 7065-2024</t>
+        </is>
+      </c>
+      <c r="B803" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C803" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>TIERP</t>
+        </is>
+      </c>
+      <c r="G803" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H803" t="n">
+        <v>0</v>
+      </c>
+      <c r="I803" t="n">
+        <v>0</v>
+      </c>
+      <c r="J803" t="n">
+        <v>0</v>
+      </c>
+      <c r="K803" t="n">
+        <v>0</v>
+      </c>
+      <c r="L803" t="n">
+        <v>0</v>
+      </c>
+      <c r="M803" t="n">
+        <v>0</v>
+      </c>
+      <c r="N803" t="n">
+        <v>0</v>
+      </c>
+      <c r="O803" t="n">
+        <v>0</v>
+      </c>
+      <c r="P803" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q803" t="n">
+        <v>0</v>
+      </c>
+      <c r="R803" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z803"/>
+  <dimension ref="A1:Z804"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>44970</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>45105</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45181</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>43627</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>44215</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>44651</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>44995</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45184</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>44980</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44977</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45252</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>43381</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44950</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44970</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45040</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45236</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>44361</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>44552</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>44958</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>45176</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45180</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>43768</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>44550</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>44551</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44662</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>44875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>44966</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>44970</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
         <v>44984</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>43488</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>43549</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>43664</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>43777</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>44468</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>44636</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>44651</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>44846</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44887</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>44950</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>44956</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45009</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>45105</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         <v>45142</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45204</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         <v>45209</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>45257</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>45294</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>43403</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>43486</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>43635</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>43651</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         <v>43847</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>43850</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>43860</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>43906</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>43930</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>43931</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44218</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>44551</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44560</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44595</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44607</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44788</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44823</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         <v>44845</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>44852</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>44894</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44911</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>44960</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45005</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45160</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>45163</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>45173</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>45173</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>45183</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45208</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>45212</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>45253</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>45310</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>45310</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45335</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43336</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>43336</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>43343</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>43355</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>43367</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>43378</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>43385</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>43412</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>43416</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>43424</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>43427</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>43434</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>43438</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>43439</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>43440</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>43446</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>43446</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>43446</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>43447</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>43447</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>43450</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>43450</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9816,7 +9816,7 @@
         <v>43451</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>43462</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>43475</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>43476</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>43486</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>43488</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>43495</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>43496</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>43500</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>43514</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>43517</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>43521</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>43522</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>43528</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>43529</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>43536</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>43539</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>43559</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>43567</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>43606</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>43606</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>43612</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>43612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>43633</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>43641</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>43642</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>43651</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>43656</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>43656</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>43668</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>43676</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>43686</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>43692</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>43692</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>43706</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>43707</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>43711</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>43733</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>43733</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>43734</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>43738</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>43740</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>43741</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>43746</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>43747</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>43756</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>43761</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>43770</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>43770</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>43774</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12949,7 +12949,7 @@
         <v>43780</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>43780</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>43780</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>43795</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>43796</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>43797</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>43797</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>43801</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>43801</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>43802</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>43809</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>43809</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>43812</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13700,7 +13700,7 @@
         <v>43829</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>43839</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>43843</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>43853</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>43853</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>43859</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>43859</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>43874</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>43875</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>43878</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>43880</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>43882</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>43893</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>43896</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>43900</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>43901</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>43906</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>43913</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>43913</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>43930</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>43936</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>43938</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>43957</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15071,7 +15071,7 @@
         <v>43958</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>43963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15190,7 +15190,7 @@
         <v>43964</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>43965</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>43983</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>43985</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>43985</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>43985</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>43993</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44006</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>44007</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>44008</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>44013</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44021</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44022</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>44025</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44029</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44043</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44049</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>44056</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>44056</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44056</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>44085</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>44088</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44097</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>44106</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>44111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         <v>44116</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>44123</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>44144</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>44150</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>44151</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44154</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>44154</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>44164</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>44165</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>44166</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>44172</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44172</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>44200</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>44208</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>44208</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>44211</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44214</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>44215</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>44218</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>44231</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44237</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>44266</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>44266</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>44270</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>44272</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44281</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>44285</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>44286</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>44286</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>44290</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>44291</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>44308</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>44309</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>44323</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>44333</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>44335</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44335</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>44337</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>44337</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>44337</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>44347</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>44357</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>44358</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>44358</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>44365</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>44368</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>44371</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>44376</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>44382</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>44389</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>44389</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>44417</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44418</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>44421</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44431</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44434</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>44438</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44439</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>44439</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>44439</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>44440</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44441</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>44446</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44452</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44452</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
         <v>44452</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>44452</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20892,7 +20892,7 @@
         <v>44453</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>44453</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44453</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>44459</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>44463</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>44469</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21368,7 +21368,7 @@
         <v>44469</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>44469</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>44474</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21539,7 +21539,7 @@
         <v>44480</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21596,7 +21596,7 @@
         <v>44480</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>44481</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>44482</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>44491</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>44491</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44496</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>44496</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>44497</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>44504</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>44515</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>44516</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>44518</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>44529</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>44532</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>44543</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>44547</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>44548</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>44560</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>44571</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>44578</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>44579</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>44579</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44580</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>44581</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44581</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>44581</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44588</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>44592</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44593</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44594</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>44594</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>44594</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44597</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44600</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44603</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44616</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44617</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44620</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44627</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44627</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44627</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44627</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44631</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44631</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44634</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44636</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44636</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44638</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>44641</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>44644</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>44648</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>44648</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>44656</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>44670</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44672</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>44677</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>44677</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>44684</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24972,7 +24972,7 @@
         <v>44684</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44686</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>44687</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>44689</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>44696</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25262,7 +25262,7 @@
         <v>44698</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>44700</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>44701</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>44701</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44701</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44704</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44704</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>44704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25790,7 +25790,7 @@
         <v>44704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25847,7 +25847,7 @@
         <v>44705</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44708</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>44708</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44713</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>44713</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>44715</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>44722</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>44725</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>44726</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>44728</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>44732</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>44734</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>44734</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44735</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44739</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>44739</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>44742</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>44743</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26943,7 +26943,7 @@
         <v>44743</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>44747</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27062,7 +27062,7 @@
         <v>44748</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27119,7 +27119,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>44749</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27233,7 +27233,7 @@
         <v>44750</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>44750</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>44755</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>44756</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>44756</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>44756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>44769</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>44769</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>44778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>44778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>44781</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>44781</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27984,7 +27984,7 @@
         <v>44788</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>44790</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28098,7 +28098,7 @@
         <v>44792</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28155,7 +28155,7 @@
         <v>44804</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>44804</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>44811</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28331,7 +28331,7 @@
         <v>44819</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44819</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28445,7 +28445,7 @@
         <v>44824</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44827</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44837</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44837</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44841</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44841</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28787,7 +28787,7 @@
         <v>44843</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>44845</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>44846</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28963,7 +28963,7 @@
         <v>44847</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>44853</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>44853</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>44853</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29191,7 +29191,7 @@
         <v>44858</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>44858</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>44858</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>44859</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
         <v>44859</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>44861</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>44865</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29781,7 +29781,7 @@
         <v>44868</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>44871</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>44874</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>44880</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>44880</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30071,7 +30071,7 @@
         <v>44880</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>44881</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>44883</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30242,7 +30242,7 @@
         <v>44886</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>44887</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>44887</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>44887</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>44888</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>44890</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>44892</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>44894</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>44894</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>44894</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>44894</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>44896</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>44896</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>44900</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>44900</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31107,7 +31107,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31164,7 +31164,7 @@
         <v>44901</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>44902</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>44903</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>44906</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>44906</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31454,7 +31454,7 @@
         <v>44907</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31511,7 +31511,7 @@
         <v>44907</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44908</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44909</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44909</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44911</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>44916</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>44916</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>44917</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>44917</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>44917</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>44922</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>44924</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>44924</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>44928</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>44929</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32381,7 +32381,7 @@
         <v>44936</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>44937</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>44939</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>44942</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32666,7 +32666,7 @@
         <v>44944</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>44945</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>44945</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32837,7 +32837,7 @@
         <v>44945</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44950</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>44950</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>44953</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33065,7 +33065,7 @@
         <v>44953</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44956</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44956</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33241,7 +33241,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>44956</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>44959</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44964</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44964</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>44964</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>44964</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33655,7 +33655,7 @@
         <v>44964</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>44964</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44964</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>44964</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>44964</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44964</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44965</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44965</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>44966</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44966</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44966</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44971</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>44971</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44972</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>44973</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>44978</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44978</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>44978</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>44979</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34897,7 +34897,7 @@
         <v>44980</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>44980</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35011,7 +35011,7 @@
         <v>44980</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>44981</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>44984</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>44986</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>44986</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>44986</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>44988</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44991</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>44991</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>44994</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>45005</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45005</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45005</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>45005</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>45005</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45005</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45005</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>45005</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45006</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45009</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45009</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45013</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>45013</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36392,7 +36392,7 @@
         <v>45020</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45021</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45022</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45022</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45027</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45027</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45028</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45029</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36930,7 +36930,7 @@
         <v>45030</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>45030</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45033</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45040</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45040</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45040</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>45040</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45040</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45041</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>45043</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37597,7 +37597,7 @@
         <v>45046</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37654,7 +37654,7 @@
         <v>45046</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>45046</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         <v>45048</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37830,7 +37830,7 @@
         <v>45048</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45049</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45051</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45055</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38063,7 +38063,7 @@
         <v>45057</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45057</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38182,7 +38182,7 @@
         <v>45057</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38239,7 +38239,7 @@
         <v>45058</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45058</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>45058</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>45061</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>45061</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45062</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
         <v>45063</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38653,7 +38653,7 @@
         <v>45063</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45070</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45071</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45072</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45075</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45075</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>45079</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>45080</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45090</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39191,7 +39191,7 @@
         <v>45091</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45092</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45092</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45092</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39424,7 +39424,7 @@
         <v>45096</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>45096</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>45096</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45098</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>45099</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39729,7 +39729,7 @@
         <v>45103</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45104</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45104</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>45105</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>45105</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40024,7 +40024,7 @@
         <v>45105</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40081,7 +40081,7 @@
         <v>45105</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45105</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>45105</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>45105</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40309,7 +40309,7 @@
         <v>45106</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40366,7 +40366,7 @@
         <v>45114</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45114</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45119</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>45121</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>45127</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45128</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>45128</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45130</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45133</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>45135</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45135</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41043,7 +41043,7 @@
         <v>45135</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>45138</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41167,7 +41167,7 @@
         <v>45146</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45148</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41291,7 +41291,7 @@
         <v>45153</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45161</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45161</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45161</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41534,7 +41534,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45162</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>45162</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>45163</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>45163</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>45163</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41886,7 +41886,7 @@
         <v>45166</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41943,7 +41943,7 @@
         <v>45166</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42000,7 +42000,7 @@
         <v>45166</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42114,7 +42114,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45167</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>45168</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42290,7 +42290,7 @@
         <v>45170</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         <v>45170</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42414,7 +42414,7 @@
         <v>45173</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45173</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45173</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42600,7 +42600,7 @@
         <v>45174</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45174</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>45174</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>45176</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>45176</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>45180</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>45181</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>45181</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>45182</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45182</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45187</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>45188</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43314,7 +43314,7 @@
         <v>45189</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43376,7 +43376,7 @@
         <v>45189</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>45190</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>45190</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>45190</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45190</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43671,7 +43671,7 @@
         <v>45190</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43733,7 +43733,7 @@
         <v>45191</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43795,7 +43795,7 @@
         <v>45191</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>45194</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45197</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45198</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44033,7 +44033,7 @@
         <v>45201</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45203</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45203</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44219,7 +44219,7 @@
         <v>45204</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>45204</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>45204</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>45209</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>45209</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45217</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>45217</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>45218</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45222</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45222</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>45223</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45518,7 +45518,7 @@
         <v>45223</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45575,7 +45575,7 @@
         <v>45224</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>45226</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45229</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45803,7 +45803,7 @@
         <v>45229</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>45230</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45922,7 +45922,7 @@
         <v>45232</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>45233</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46041,7 +46041,7 @@
         <v>45237</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46098,7 +46098,7 @@
         <v>45238</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45239</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46217,7 +46217,7 @@
         <v>45239</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>45239</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45239</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>45242</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46450,7 +46450,7 @@
         <v>45243</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45243</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46569,7 +46569,7 @@
         <v>45244</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45244</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46683,7 +46683,7 @@
         <v>45244</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46745,7 +46745,7 @@
         <v>45245</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>45245</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>45245</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>45246</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46978,7 +46978,7 @@
         <v>45246</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45246</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45247</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>45247</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47211,7 +47211,7 @@
         <v>45247</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>45247</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47325,7 +47325,7 @@
         <v>45247</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47382,7 +47382,7 @@
         <v>45247</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47439,7 +47439,7 @@
         <v>45251</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45252</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45252</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45252</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47677,7 +47677,7 @@
         <v>45253</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>45253</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>45253</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47848,7 +47848,7 @@
         <v>45257</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>45257</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45257</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48019,7 +48019,7 @@
         <v>45258</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48076,7 +48076,7 @@
         <v>45258</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>45259</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48195,7 +48195,7 @@
         <v>45259</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>45261</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>45265</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45265</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45265</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>45275</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48542,7 +48542,7 @@
         <v>45275</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45275</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45275</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>45279</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>45279</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>45279</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48889,7 +48889,7 @@
         <v>45279</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45279</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45281</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45281</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>45281</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>45281</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45282</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>45282</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>45282</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>45296</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49459,7 +49459,7 @@
         <v>45296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>45301</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>45301</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>45301</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>45307</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49744,7 +49744,7 @@
         <v>45308</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49801,7 +49801,7 @@
         <v>45308</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45310</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45312</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45314</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45316</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50086,7 +50086,7 @@
         <v>45320</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45330</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50200,7 +50200,7 @@
         <v>45338</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         <v>45338</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45343</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50361,7 +50361,7 @@
       </c>
       <c r="R802" s="2" t="inlineStr"/>
     </row>
-    <row r="803">
+    <row r="803" ht="15" customHeight="1">
       <c r="A803" t="inlineStr">
         <is>
           <t>A 7065-2024</t>
@@ -50371,7 +50371,7 @@
         <v>45343</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50417,6 +50417,63 @@
         <v>0</v>
       </c>
       <c r="R803" s="2" t="inlineStr"/>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>A 7127-2024</t>
+        </is>
+      </c>
+      <c r="B804" s="1" t="n">
+        <v>45344</v>
+      </c>
+      <c r="C804" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>TIERP</t>
+        </is>
+      </c>
+      <c r="G804" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H804" t="n">
+        <v>0</v>
+      </c>
+      <c r="I804" t="n">
+        <v>0</v>
+      </c>
+      <c r="J804" t="n">
+        <v>0</v>
+      </c>
+      <c r="K804" t="n">
+        <v>0</v>
+      </c>
+      <c r="L804" t="n">
+        <v>0</v>
+      </c>
+      <c r="M804" t="n">
+        <v>0</v>
+      </c>
+      <c r="N804" t="n">
+        <v>0</v>
+      </c>
+      <c r="O804" t="n">
+        <v>0</v>
+      </c>
+      <c r="P804" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q804" t="n">
+        <v>0</v>
+      </c>
+      <c r="R804" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -569,7 +569,7 @@
         <v>44970</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>45105</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45181</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>43627</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>44215</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>44651</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>44995</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45184</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>44980</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44977</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45252</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>43381</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44950</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44970</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45040</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45236</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45345</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>44361</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>44552</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44958</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45176</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45180</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>43768</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>44550</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>44551</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44662</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44875</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>44966</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44970</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>44984</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>43488</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>43549</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>43664</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43777</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44468</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44636</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44651</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44846</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>44887</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44950</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45009</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45105</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45142</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>45204</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45209</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45257</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>45294</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>43403</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>43486</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43635</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>43651</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>43847</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>43850</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>43860</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>43906</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43930</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43931</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44218</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44551</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44560</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>44595</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>44607</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44788</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44823</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44845</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44894</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>44911</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44960</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>45005</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45160</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45163</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45173</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45173</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45183</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>45208</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45212</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45253</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45310</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>45310</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45335</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>43336</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>43336</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>43343</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>43355</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43367</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>43371</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43378</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43385</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43412</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43416</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>43419</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43434</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43439</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43440</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>43446</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>43446</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>43446</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43447</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>43447</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>43450</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43450</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43451</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>43462</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43475</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43476</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43486</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>43488</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>43495</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>43496</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>43500</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>43517</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>43522</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>43528</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>43529</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>43539</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>43567</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>43606</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>43606</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>43612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>43612</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43642</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>43651</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43656</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>43656</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43668</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43676</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>43686</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>43692</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>43692</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>43706</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>43707</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>43711</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43733</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43733</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43734</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>43738</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>43740</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>43741</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>43746</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43747</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43756</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>43761</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>43770</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43770</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>43774</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43780</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>43780</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>43780</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>43795</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>43796</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>43797</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>43797</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>43801</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>43801</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>43802</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>43809</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>43809</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>43812</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>43829</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43839</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43843</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43853</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43853</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43859</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43859</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>43874</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>43875</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>43878</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>43880</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43882</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>43893</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>43896</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>43900</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>43906</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>43913</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>43913</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43938</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>43958</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>43964</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43965</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43983</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43985</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43985</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43985</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43993</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>44008</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>44013</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44021</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44022</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>44025</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>44029</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44043</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44049</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44056</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44056</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44056</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>44085</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44088</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44097</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>44106</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44111</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44116</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44123</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44144</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44150</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44151</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44154</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44154</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44164</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44165</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44166</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>44172</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44172</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44200</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>44208</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44208</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44211</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44214</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44215</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44218</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44231</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44237</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44266</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>44266</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>44270</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>44272</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44281</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44285</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44286</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>44286</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>44290</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>44291</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44308</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44309</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>44323</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>44333</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>44335</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44335</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44337</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44337</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44337</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44347</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44357</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44358</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44358</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44365</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44368</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44371</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44376</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44382</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44389</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>44389</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>44417</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44418</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44421</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44421</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44431</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>44434</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>44438</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>44439</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44439</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44439</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44446</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>44452</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>44452</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>44452</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>44452</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>44453</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>44453</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>44453</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44459</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44459</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44463</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44469</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44469</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44469</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44474</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44480</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44480</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44481</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44482</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44491</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44491</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44496</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44496</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44497</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44504</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44515</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44516</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44518</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44529</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>44532</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44543</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>44547</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>44548</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>44560</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>44571</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44578</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>44579</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44579</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>44580</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>44581</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44581</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>44581</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44588</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>44592</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>44594</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>44594</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44594</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44597</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44600</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>44603</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44616</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>44617</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>44620</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>44627</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>44627</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>44627</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>44627</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>44631</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>44631</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>44634</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>44636</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>44636</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>44638</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>44641</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>44644</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>44648</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>44648</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>44656</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44670</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>44672</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>44677</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>44677</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44684</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44684</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>44686</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>44687</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44689</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>44696</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>44698</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>44700</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44701</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>44701</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>44701</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>44704</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>44704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44704</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44705</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44708</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>44708</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44713</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>44713</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44715</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>44722</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>44725</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44726</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>44728</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>44732</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44734</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44734</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44735</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44739</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44739</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44742</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44743</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44743</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44748</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44749</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44749</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44750</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44750</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44755</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44756</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44756</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44769</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44769</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>44778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>44778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>44778</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44781</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44781</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44788</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44790</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44792</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44804</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44811</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44819</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>44819</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44824</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>44827</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>44837</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>44837</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>44841</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>44841</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>44843</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>44845</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44846</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44847</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44853</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>44853</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44853</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44858</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44858</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44858</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>44859</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>44859</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>44861</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44865</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44868</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44871</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44874</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44880</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44880</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44880</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44881</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44883</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44886</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44887</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44887</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44887</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44888</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44890</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44892</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44894</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44894</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44894</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>44894</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>44896</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>44896</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44900</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>44900</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>44901</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>44902</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44903</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>44906</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>44906</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>44907</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>44907</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>44908</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44909</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44909</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44911</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44916</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>44916</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44917</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44917</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44917</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>44922</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>44924</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>44924</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>44928</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>44929</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>44936</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>44937</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44939</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44942</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44944</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44945</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44945</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>44945</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44950</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44950</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44953</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>44953</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44956</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44956</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44956</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44959</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44964</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44964</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44964</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>44964</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>44964</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44964</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44964</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44964</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>44964</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44964</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44965</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         <v>44965</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>44966</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>44966</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>44966</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>44971</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44971</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44972</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44973</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44978</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44978</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44978</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44978</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>44979</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>44980</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>44980</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44980</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>44981</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>44984</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>44986</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44986</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44986</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44988</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>44991</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>44991</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44994</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45005</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45005</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45005</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45005</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45005</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45005</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45005</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45005</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45006</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45009</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45009</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45013</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45013</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45020</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45021</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45022</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45022</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45027</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45027</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45028</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45029</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45030</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45030</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45033</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45040</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>45040</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>45040</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45040</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45040</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45041</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45043</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>45046</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45046</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>45046</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45048</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45048</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45049</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45051</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45055</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>45057</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45057</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45057</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45058</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>45058</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>45058</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45061</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45061</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45062</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45063</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45063</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45070</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>45071</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45072</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45075</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45075</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45079</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45080</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45090</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45091</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45092</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45092</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45092</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45096</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>45096</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45096</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45098</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45099</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45103</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>45104</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45104</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>45105</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45105</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>45105</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45105</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45105</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>45105</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45105</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45106</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>45114</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>45114</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>45119</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45121</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45128</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45128</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45130</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45133</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45135</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>45135</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45135</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45138</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45146</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45153</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45161</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45161</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45162</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45162</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45163</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45163</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>45163</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45166</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>45166</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45167</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45168</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45170</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45170</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42512,7 +42512,7 @@
         <v>45173</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45173</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45173</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45174</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>45174</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45174</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>45176</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45176</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45180</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45181</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45181</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>45182</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45182</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45187</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45188</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45189</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45189</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45190</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45190</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45190</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45190</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>45190</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>45191</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45191</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45194</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>45197</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>45198</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45201</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>45203</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45203</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45204</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>45204</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45204</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45209</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45209</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45217</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45217</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45218</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45222</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45222</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45223</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45223</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45224</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>45226</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45226</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>45229</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45229</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45230</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45232</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45233</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45237</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45238</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45239</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45239</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>45239</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45239</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46491,7 +46491,7 @@
         <v>45242</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45243</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>45243</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45244</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45244</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45244</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45245</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45245</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45245</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45246</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>45246</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>45246</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45247</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45247</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>45247</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45247</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45247</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45247</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45251</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45252</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>45252</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45252</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45253</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>45253</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45253</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45257</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45257</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45257</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>45258</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45258</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45259</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>45259</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45261</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>45265</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>45265</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45265</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45275</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>45275</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>45275</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>45275</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45279</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45279</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45279</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45279</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45279</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45281</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45281</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45281</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45281</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45282</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45282</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45282</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>45296</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>45301</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45301</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45301</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49785,7 +49785,7 @@
         <v>45307</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45308</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45308</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45310</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45312</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45314</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45316</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45320</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45330</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45338</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>45338</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50405,14 +50405,14 @@
     <row r="803" ht="15" customHeight="1">
       <c r="A803" t="inlineStr">
         <is>
-          <t>A 7048-2024</t>
+          <t>A 7065-2024</t>
         </is>
       </c>
       <c r="B803" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         </is>
       </c>
       <c r="G803" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="H803" t="n">
         <v>0</v>
@@ -50462,14 +50462,14 @@
     <row r="804" ht="15" customHeight="1">
       <c r="A804" t="inlineStr">
         <is>
-          <t>A 7065-2024</t>
+          <t>A 7048-2024</t>
         </is>
       </c>
       <c r="B804" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         </is>
       </c>
       <c r="G804" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="H804" t="n">
         <v>0</v>
@@ -50526,7 +50526,7 @@
         <v>45344</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -569,7 +569,7 @@
         <v>44970</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>45105</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45181</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>43627</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>44215</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>44651</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>44995</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45184</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>44980</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44977</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45252</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>43381</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44950</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44970</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45040</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45236</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45345</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>44361</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>44552</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44958</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45176</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45180</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>43768</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>44550</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>44551</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44662</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44875</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>44966</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44970</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>44984</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>43488</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>43549</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>43664</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43777</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44468</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44636</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44651</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44846</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>44887</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44950</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45009</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45105</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45142</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>45204</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45209</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45257</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>45294</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>43403</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>43486</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43635</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>43651</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>43847</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>43850</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>43860</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>43906</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43930</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43931</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44218</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44551</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44560</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>44595</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>44607</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44788</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44823</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44845</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44894</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>44911</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44960</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>45005</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45160</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45163</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45173</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45173</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45183</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>45208</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45212</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45253</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45310</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>45310</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45335</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>43336</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>43336</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>43343</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>43355</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43367</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>43371</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43378</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43385</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43412</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43416</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>43419</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43434</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43439</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43440</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>43446</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>43446</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>43446</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43447</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>43447</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>43450</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43450</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43451</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>43462</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43475</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43476</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43486</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>43488</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>43495</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>43496</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>43500</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>43517</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>43522</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>43528</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>43529</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>43539</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>43567</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>43606</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>43606</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>43612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>43612</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43642</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>43651</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43656</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>43656</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43668</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43676</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>43686</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>43692</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>43692</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>43706</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>43707</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>43711</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43733</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43733</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43734</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>43738</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>43740</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>43741</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>43746</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43747</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43756</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>43761</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>43770</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43770</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>43774</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43780</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>43780</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>43780</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>43795</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>43796</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>43797</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>43797</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>43801</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>43801</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>43802</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>43809</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>43809</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>43812</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>43829</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43839</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43843</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43853</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43853</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43859</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43859</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>43874</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>43875</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>43878</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>43880</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43882</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>43893</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>43896</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>43900</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>43906</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>43913</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>43913</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43938</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>43958</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>43964</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43965</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43983</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43985</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43985</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43985</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43993</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>44008</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>44013</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44021</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44022</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>44025</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>44029</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44043</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44049</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44056</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44056</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44056</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>44085</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44088</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44097</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>44106</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44111</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44116</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44123</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44144</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44150</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44151</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44154</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44154</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44164</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44165</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44166</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>44172</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44172</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44200</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>44208</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44208</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44211</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44214</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44215</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44218</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44231</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44237</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44266</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>44266</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>44270</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>44272</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44281</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44285</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44286</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>44286</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>44290</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>44291</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44308</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44309</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>44323</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>44333</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>44335</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44335</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44337</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44337</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44337</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44347</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44357</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44358</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44358</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44365</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44368</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44371</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44376</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44382</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44389</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>44389</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>44417</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44418</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44421</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44421</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44431</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>44434</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>44438</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>44439</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44439</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44439</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44446</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>44452</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>44452</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>44452</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>44452</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>44453</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>44453</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>44453</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44459</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44459</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44463</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44469</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44469</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44469</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44474</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44480</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44480</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44481</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44482</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44491</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44491</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44496</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44496</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44497</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44504</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44515</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44516</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44518</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44529</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>44532</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44543</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>44547</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>44548</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>44560</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>44571</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44578</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>44579</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44579</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>44580</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>44581</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44581</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>44581</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44588</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>44592</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>44594</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>44594</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44594</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44597</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44600</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>44603</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44616</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>44617</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>44620</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>44627</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>44627</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>44627</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>44627</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>44631</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>44631</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>44634</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>44636</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>44636</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>44638</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>44641</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>44644</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>44648</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>44648</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>44656</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44670</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>44672</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>44677</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>44677</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44684</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44684</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>44686</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>44687</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44689</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>44696</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>44698</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>44700</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44701</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>44701</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>44701</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>44704</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>44704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44704</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44705</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44708</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>44708</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44713</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>44713</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44715</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>44722</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>44725</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44726</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>44728</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>44732</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44734</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44734</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44735</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44739</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44739</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44742</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44743</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44743</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44748</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44749</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44749</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44750</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44750</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44755</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44756</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44756</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44769</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44769</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>44778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>44778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>44778</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44781</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44781</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44788</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44790</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44792</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44804</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44811</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44819</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>44819</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44824</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>44827</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>44837</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>44837</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>44841</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>44841</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>44843</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>44845</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44846</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44847</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44853</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>44853</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44853</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44858</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44858</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44858</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>44859</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>44859</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>44861</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44865</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44868</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44871</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44874</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44880</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44880</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44880</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44881</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44883</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44886</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44887</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44887</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44887</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44888</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44890</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44892</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44894</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44894</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44894</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>44894</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>44896</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>44896</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44900</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>44900</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>44901</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>44902</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44903</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>44906</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>44906</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>44907</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>44907</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>44908</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44909</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44909</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44911</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44916</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>44916</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44917</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44917</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44917</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>44922</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>44924</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>44924</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>44928</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>44929</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>44936</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>44937</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44939</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44942</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44944</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44945</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44945</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>44945</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44950</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44950</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44953</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>44953</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44956</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44956</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44956</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44959</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44964</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44964</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44964</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>44964</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>44964</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44964</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44964</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44964</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>44964</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44964</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44965</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         <v>44965</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>44966</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>44966</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>44966</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>44971</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44971</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44972</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44973</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44978</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44978</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44978</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44978</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>44979</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>44980</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>44980</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44980</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>44981</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>44984</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>44986</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44986</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44986</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44988</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>44991</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>44991</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44994</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45005</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45005</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45005</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45005</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45005</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45005</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45005</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45005</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45006</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45009</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45009</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45013</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45013</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45020</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45021</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45022</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45022</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45027</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45027</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45028</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45029</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45030</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45030</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45033</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45040</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>45040</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>45040</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45040</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45040</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45041</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45043</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>45046</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45046</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>45046</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45048</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45048</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45049</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45051</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45055</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>45057</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45057</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45057</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45058</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>45058</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>45058</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45061</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45061</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45062</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45063</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45063</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45070</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>45071</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45072</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45075</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45075</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45079</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45080</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45090</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45091</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45092</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45092</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45092</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45096</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>45096</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45096</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45098</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45099</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45103</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>45104</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45104</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>45105</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45105</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>45105</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45105</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45105</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>45105</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45105</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45106</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>45114</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>45114</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>45119</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45121</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45128</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45128</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45130</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45133</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45135</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>45135</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45135</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45138</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45146</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45153</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45161</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45161</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45162</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45162</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45163</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45163</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>45163</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45166</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>45166</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45167</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45168</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45170</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45170</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42512,7 +42512,7 @@
         <v>45173</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45173</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45173</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45174</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>45174</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45174</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>45176</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45176</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45180</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45181</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45181</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>45182</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45182</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45187</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45188</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45189</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45189</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45190</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45190</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45190</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45190</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>45190</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>45191</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45191</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45194</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>45197</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>45198</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45201</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>45203</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45203</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45204</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>45204</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45204</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45209</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45209</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45217</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45217</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45218</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45222</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45222</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45223</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45223</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45224</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>45226</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45226</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>45229</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45229</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45230</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45232</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45233</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45237</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45238</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45239</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45239</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>45239</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45239</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46491,7 +46491,7 @@
         <v>45242</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45243</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>45243</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45244</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45244</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45244</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45245</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45245</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45245</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45246</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>45246</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>45246</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45247</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45247</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>45247</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45247</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45247</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45247</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45251</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45252</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>45252</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45252</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45253</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>45253</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45253</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45257</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45257</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45257</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>45258</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45258</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45259</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>45259</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45261</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>45265</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>45265</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45265</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45275</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>45275</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>45275</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>45275</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45279</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45279</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45279</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45279</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45279</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45281</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45281</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45281</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45281</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45282</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45282</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45282</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>45296</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>45301</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45301</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45301</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49785,7 +49785,7 @@
         <v>45307</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45308</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45308</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45310</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45312</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45314</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45316</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45320</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45330</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50291,14 +50291,14 @@
     <row r="801" ht="15" customHeight="1">
       <c r="A801" t="inlineStr">
         <is>
-          <t>A 6395-2024</t>
+          <t>A 6385-2024</t>
         </is>
       </c>
       <c r="B801" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         </is>
       </c>
       <c r="G801" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="H801" t="n">
         <v>0</v>
@@ -50348,14 +50348,14 @@
     <row r="802" ht="15" customHeight="1">
       <c r="A802" t="inlineStr">
         <is>
-          <t>A 6385-2024</t>
+          <t>A 6395-2024</t>
         </is>
       </c>
       <c r="B802" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50368,7 +50368,7 @@
         </is>
       </c>
       <c r="G802" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="H802" t="n">
         <v>0</v>
@@ -50405,14 +50405,14 @@
     <row r="803" ht="15" customHeight="1">
       <c r="A803" t="inlineStr">
         <is>
-          <t>A 7065-2024</t>
+          <t>A 7048-2024</t>
         </is>
       </c>
       <c r="B803" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         </is>
       </c>
       <c r="G803" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="H803" t="n">
         <v>0</v>
@@ -50462,14 +50462,14 @@
     <row r="804" ht="15" customHeight="1">
       <c r="A804" t="inlineStr">
         <is>
-          <t>A 7048-2024</t>
+          <t>A 7065-2024</t>
         </is>
       </c>
       <c r="B804" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         </is>
       </c>
       <c r="G804" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="H804" t="n">
         <v>0</v>
@@ -50526,7 +50526,7 @@
         <v>45344</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -569,7 +569,7 @@
         <v>44970</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>45105</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45181</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>43627</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>44215</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>44651</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>44995</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45184</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>44980</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44977</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45252</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>43381</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44950</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44970</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45040</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45236</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45345</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>44361</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>44552</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44958</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45176</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45180</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>43768</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>44550</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>44551</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44662</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44875</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>44966</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44970</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>44984</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>43488</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>43549</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>43664</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43777</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44468</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44636</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44651</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44846</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>44887</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44950</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45009</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45105</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45142</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>45204</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45209</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45257</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>45294</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>43403</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>43486</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43635</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>43651</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>43847</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>43850</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>43860</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>43906</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43930</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43931</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44218</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44551</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44560</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>44595</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>44607</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44788</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44823</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44845</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44894</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>44911</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44960</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>45005</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45160</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45163</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45173</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45173</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45183</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>45208</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45212</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45253</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45310</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>45310</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45335</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>43336</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>43336</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>43343</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>43355</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43367</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>43371</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43378</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43385</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43412</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43416</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>43419</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43434</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43439</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43440</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>43446</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>43446</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>43446</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43447</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>43447</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>43450</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43450</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43451</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>43462</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43475</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43476</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43486</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>43488</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>43495</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>43496</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>43500</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>43517</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>43522</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>43528</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>43529</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>43539</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>43567</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>43606</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>43606</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>43612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>43612</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43642</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>43651</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43656</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>43656</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43668</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43676</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>43686</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>43692</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>43692</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>43706</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>43707</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>43711</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43733</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43733</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43734</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>43738</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>43740</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>43741</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>43746</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43747</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43756</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>43761</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>43770</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43770</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>43774</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43780</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>43780</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>43780</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>43795</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>43796</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>43797</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>43797</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>43801</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>43801</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>43802</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>43809</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>43809</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>43812</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>43829</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43839</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43843</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43853</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43853</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43859</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43859</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>43874</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>43875</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>43878</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>43880</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43882</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>43893</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>43896</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>43900</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>43906</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>43913</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>43913</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43938</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>43958</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>43964</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43965</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43983</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43985</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43985</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43985</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43993</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>44008</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>44013</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44021</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44022</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>44025</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>44029</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44043</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44049</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44056</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44056</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44056</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>44085</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44088</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44097</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>44106</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44111</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44116</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44123</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44144</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44150</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44151</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44154</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44154</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44164</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44165</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44166</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>44172</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44172</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44200</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>44208</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44208</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44211</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44214</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44215</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44218</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44231</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44237</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44266</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>44266</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>44270</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>44272</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44281</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44285</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44286</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>44286</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>44290</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>44291</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44308</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44309</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>44323</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>44333</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>44335</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44335</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44337</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44337</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44337</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44347</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44357</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44358</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44358</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44365</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44368</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44371</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44376</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44382</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44389</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>44389</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>44417</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44418</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44421</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44421</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44431</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>44434</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>44438</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>44439</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44439</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44439</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44446</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>44452</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>44452</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>44452</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>44452</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>44453</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>44453</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>44453</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44459</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44459</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44463</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44469</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44469</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44469</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44474</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44480</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44480</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44481</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44482</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44491</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44491</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44496</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44496</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44497</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44504</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44515</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44516</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44518</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44529</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>44532</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44543</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>44547</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>44548</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>44560</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>44571</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44578</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>44579</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44579</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>44580</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>44581</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44581</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>44581</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44588</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>44592</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>44594</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>44594</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44594</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44597</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44600</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>44603</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44616</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>44617</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>44620</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>44627</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>44627</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>44627</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>44627</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>44631</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>44631</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>44634</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>44636</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>44636</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>44638</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>44641</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>44644</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>44648</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>44648</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>44656</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44670</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>44672</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>44677</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>44677</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44684</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44684</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>44686</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>44687</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44689</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>44696</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>44698</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>44700</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44701</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>44701</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>44701</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>44704</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>44704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44704</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44705</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44708</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>44708</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44713</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>44713</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44715</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>44722</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>44725</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44726</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>44728</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>44732</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44734</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44734</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44735</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44739</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44739</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44742</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44743</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44743</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44748</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44749</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44749</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44750</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44750</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44755</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44756</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44756</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44769</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44769</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>44778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>44778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>44778</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44781</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44781</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44788</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44790</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44792</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44804</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44811</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44819</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>44819</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44824</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>44827</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>44837</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>44837</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>44841</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>44841</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>44843</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>44845</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44846</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44847</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44853</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>44853</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44853</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44858</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44858</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44858</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>44859</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>44859</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>44861</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44865</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44868</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44871</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44874</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44880</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44880</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44880</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44881</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44883</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44886</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44887</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44887</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44887</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44888</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44890</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44892</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44894</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44894</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44894</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>44894</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>44896</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>44896</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44900</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>44900</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>44901</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>44902</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44903</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>44906</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>44906</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>44907</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>44907</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>44908</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44909</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44909</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44911</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44916</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>44916</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44917</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44917</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44917</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>44922</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>44924</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>44924</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>44928</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>44929</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>44936</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>44937</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44939</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44942</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44944</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44945</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44945</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>44945</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44950</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44950</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44953</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>44953</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44956</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44956</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44956</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44959</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44964</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44964</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44964</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>44964</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>44964</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44964</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44964</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44964</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>44964</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44964</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44965</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         <v>44965</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>44966</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>44966</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>44966</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>44971</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44971</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44972</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44973</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44978</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44978</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44978</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44978</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>44979</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>44980</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>44980</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44980</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>44981</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>44984</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>44986</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44986</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44986</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44988</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>44991</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>44991</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44994</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45005</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45005</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45005</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45005</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45005</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45005</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45005</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45005</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45006</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45009</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45009</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45013</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45013</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45020</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45021</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45022</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45022</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45027</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45027</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45028</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45029</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45030</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45030</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45033</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45040</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>45040</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>45040</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45040</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45040</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45041</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45043</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>45046</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45046</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>45046</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45048</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45048</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45049</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45051</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45055</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>45057</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45057</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45057</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45058</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>45058</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>45058</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45061</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45061</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45062</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45063</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45063</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45070</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>45071</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45072</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45075</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45075</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45079</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45080</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45090</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45091</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45092</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45092</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45092</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45096</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>45096</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45096</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45098</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45099</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45103</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>45104</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45104</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>45105</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45105</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>45105</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45105</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45105</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>45105</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45105</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45106</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>45114</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>45114</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>45119</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45121</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45128</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45128</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45130</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45133</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45135</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>45135</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45135</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45138</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45146</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45153</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45161</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45161</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45162</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45162</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45163</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45163</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>45163</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45166</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>45166</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45167</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45168</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45170</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45170</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42512,7 +42512,7 @@
         <v>45173</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45173</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45173</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45174</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>45174</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45174</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>45176</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45176</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45180</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45181</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45181</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>45182</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45182</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45187</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45188</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45189</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45189</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45190</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45190</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45190</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45190</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>45190</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>45191</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45191</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45194</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>45197</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>45198</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45201</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>45203</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45203</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45204</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>45204</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45204</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45209</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45209</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45217</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45217</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45218</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45222</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45222</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45223</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45223</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45224</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>45226</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45226</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>45229</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45229</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45230</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45232</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45233</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45237</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45238</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45239</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45239</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>45239</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45239</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46491,7 +46491,7 @@
         <v>45242</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45243</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>45243</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45244</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45244</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45244</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45245</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45245</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45245</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45246</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>45246</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>45246</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45247</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45247</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>45247</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45247</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45247</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45247</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45251</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45252</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>45252</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45252</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45253</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>45253</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45253</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45257</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45257</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45257</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>45258</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45258</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45259</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>45259</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45261</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>45265</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>45265</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45265</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45275</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>45275</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>45275</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>45275</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45279</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45279</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45279</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45279</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45279</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45281</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45281</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45281</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45281</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45282</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45282</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45282</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>45296</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>45301</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45301</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45301</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49785,7 +49785,7 @@
         <v>45307</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45308</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45308</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45310</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45312</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45314</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45316</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45320</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45330</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50291,14 +50291,14 @@
     <row r="801" ht="15" customHeight="1">
       <c r="A801" t="inlineStr">
         <is>
-          <t>A 6385-2024</t>
+          <t>A 6395-2024</t>
         </is>
       </c>
       <c r="B801" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         </is>
       </c>
       <c r="G801" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="H801" t="n">
         <v>0</v>
@@ -50348,14 +50348,14 @@
     <row r="802" ht="15" customHeight="1">
       <c r="A802" t="inlineStr">
         <is>
-          <t>A 6395-2024</t>
+          <t>A 6385-2024</t>
         </is>
       </c>
       <c r="B802" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50368,7 +50368,7 @@
         </is>
       </c>
       <c r="G802" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="H802" t="n">
         <v>0</v>
@@ -50405,14 +50405,14 @@
     <row r="803" ht="15" customHeight="1">
       <c r="A803" t="inlineStr">
         <is>
-          <t>A 7048-2024</t>
+          <t>A 7065-2024</t>
         </is>
       </c>
       <c r="B803" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         </is>
       </c>
       <c r="G803" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="H803" t="n">
         <v>0</v>
@@ -50462,14 +50462,14 @@
     <row r="804" ht="15" customHeight="1">
       <c r="A804" t="inlineStr">
         <is>
-          <t>A 7065-2024</t>
+          <t>A 7048-2024</t>
         </is>
       </c>
       <c r="B804" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         </is>
       </c>
       <c r="G804" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="H804" t="n">
         <v>0</v>
@@ -50526,7 +50526,7 @@
         <v>45344</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -569,7 +569,7 @@
         <v>44970</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>45105</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45181</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>43627</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>44215</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>44651</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>44995</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45184</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>44980</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44977</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45252</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>43381</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44950</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44970</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45040</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45236</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45345</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>44361</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>44552</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44958</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45176</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45180</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>43768</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>44550</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>44551</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44662</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44875</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>44966</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44970</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>44984</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>43488</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>43549</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>43664</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43777</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44468</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44636</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44651</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44846</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>44887</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44950</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45009</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45105</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45142</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>45204</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45209</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45257</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>45294</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>43403</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>43486</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43635</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>43651</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>43847</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>43850</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>43860</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>43906</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43930</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43931</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44218</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44551</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44560</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>44595</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>44607</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44788</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44823</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44845</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44894</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>44911</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44960</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>45005</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45160</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45163</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45173</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45173</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45183</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>45208</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45212</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45253</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45310</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>45310</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45335</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>43336</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>43336</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>43343</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>43355</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43367</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>43371</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43378</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43385</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43412</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43416</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>43419</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43434</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43439</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43440</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>43446</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>43446</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>43446</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43447</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>43447</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>43450</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43450</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43451</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>43462</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43475</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43476</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43486</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>43488</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>43495</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>43496</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>43500</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>43517</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>43522</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>43528</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>43529</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>43539</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>43567</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>43606</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>43606</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>43612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>43612</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43642</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>43651</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43656</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>43656</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43668</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43676</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>43686</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>43692</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>43692</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>43706</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>43707</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>43711</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43733</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43733</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43734</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>43738</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>43740</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>43741</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>43746</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43747</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43756</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>43761</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>43770</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43770</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>43774</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43780</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>43780</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>43780</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>43795</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>43796</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>43797</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>43797</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>43801</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>43801</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>43802</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>43809</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>43809</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>43812</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>43829</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43839</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43843</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43853</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43853</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43859</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43859</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>43874</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>43875</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>43878</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>43880</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43882</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>43893</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>43896</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>43900</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>43906</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>43913</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>43913</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43938</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>43958</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>43964</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43965</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43983</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43985</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43985</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43985</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43993</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>44008</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>44013</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44021</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44022</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>44025</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>44029</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44043</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44049</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44056</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44056</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44056</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>44085</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44088</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44097</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>44106</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44111</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44116</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44123</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44144</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44150</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44151</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44154</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44154</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44164</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44165</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44166</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>44172</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44172</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44200</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>44208</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44208</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44211</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44214</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44215</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44218</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44231</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44237</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44266</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>44266</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>44270</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>44272</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44281</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44285</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44286</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>44286</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>44290</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>44291</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44308</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44309</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>44323</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>44333</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>44335</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44335</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44337</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44337</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44337</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44347</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44357</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44358</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44358</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44365</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44368</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44371</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44376</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44382</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44389</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>44389</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>44417</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44418</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44421</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44421</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44431</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>44434</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>44438</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>44439</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44439</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44439</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44446</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>44452</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>44452</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>44452</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>44452</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>44453</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>44453</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>44453</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44459</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44459</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44463</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44469</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44469</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44469</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44474</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44480</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44480</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44481</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44482</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44491</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44491</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44496</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44496</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44497</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44504</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44515</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44516</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44518</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44529</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>44532</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44543</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>44547</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>44548</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>44560</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>44571</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44578</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>44579</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44579</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>44580</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>44581</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44581</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>44581</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44588</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>44592</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>44594</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>44594</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44594</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44597</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44600</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>44603</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44616</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>44617</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>44620</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>44627</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>44627</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>44627</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>44627</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>44631</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>44631</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>44634</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>44636</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>44636</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>44638</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>44641</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>44644</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>44648</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>44648</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>44656</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44670</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>44672</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>44677</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>44677</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44684</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44684</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>44686</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>44687</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44689</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>44696</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>44698</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>44700</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44701</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>44701</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>44701</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>44704</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>44704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44704</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44705</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44708</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>44708</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44713</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>44713</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44715</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>44722</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>44725</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44726</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>44728</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>44732</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44734</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44734</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44735</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44739</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44739</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44742</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44743</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44743</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44748</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44749</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44749</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44750</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44750</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44755</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44756</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44756</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44769</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44769</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>44778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>44778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>44778</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44781</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44781</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44788</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44790</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44792</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44804</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44811</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44819</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>44819</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44824</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>44827</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>44837</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>44837</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>44841</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>44841</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>44843</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>44845</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44846</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44847</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44853</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>44853</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44853</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44858</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44858</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44858</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>44859</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>44859</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>44861</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44865</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44868</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44871</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44874</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44880</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44880</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44880</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44881</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44883</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44886</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44887</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44887</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44887</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44888</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44890</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44892</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44894</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44894</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44894</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>44894</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>44896</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>44896</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44900</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>44900</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>44901</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>44902</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44903</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>44906</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>44906</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>44907</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>44907</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>44908</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44909</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44909</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44911</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44916</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>44916</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44917</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44917</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44917</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>44922</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>44924</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>44924</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>44928</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>44929</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>44936</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>44937</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44939</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44942</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44944</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44945</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44945</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>44945</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44950</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44950</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44953</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>44953</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44956</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44956</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44956</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44959</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44964</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44964</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44964</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>44964</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>44964</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44964</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44964</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44964</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>44964</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44964</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44965</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         <v>44965</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>44966</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>44966</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>44966</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>44971</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44971</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44972</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44973</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44978</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44978</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44978</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44978</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>44979</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>44980</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>44980</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44980</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>44981</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>44984</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>44986</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44986</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44986</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44988</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>44991</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>44991</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44994</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45005</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45005</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45005</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45005</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45005</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45005</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45005</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45005</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45006</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45009</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45009</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45013</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45013</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45020</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45021</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45022</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45022</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45027</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45027</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45028</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45029</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45030</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45030</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45033</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45040</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>45040</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>45040</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45040</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45040</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45041</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45043</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>45046</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45046</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>45046</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45048</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45048</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45049</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45051</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45055</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>45057</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45057</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45057</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45058</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>45058</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>45058</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45061</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45061</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45062</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45063</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45063</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45070</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>45071</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45072</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45075</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45075</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45079</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45080</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45090</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45091</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45092</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45092</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45092</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45096</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>45096</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45096</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45098</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45099</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45103</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>45104</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45104</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>45105</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45105</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>45105</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45105</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45105</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>45105</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45105</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45106</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>45114</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>45114</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>45119</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45121</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45128</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45128</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45130</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45133</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45135</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>45135</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45135</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45138</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45146</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45153</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45161</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45161</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45162</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45162</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45163</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45163</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>45163</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45166</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>45166</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45167</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45168</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45170</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45170</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42512,7 +42512,7 @@
         <v>45173</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45173</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45173</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45174</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>45174</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45174</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>45176</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45176</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45180</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45181</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45181</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>45182</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45182</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45187</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45188</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45189</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45189</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45190</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45190</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45190</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45190</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>45190</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>45191</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45191</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45194</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>45197</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>45198</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45201</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>45203</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45203</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45204</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>45204</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45204</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45209</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45209</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45217</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45217</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45218</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45222</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45222</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45223</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45223</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45224</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>45226</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45226</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>45229</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45229</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45230</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45232</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45233</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45237</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45238</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45239</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45239</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>45239</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45239</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46491,7 +46491,7 @@
         <v>45242</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45243</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>45243</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45244</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45244</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45244</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45245</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45245</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45245</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45246</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>45246</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>45246</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45247</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45247</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>45247</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45247</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45247</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45247</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45251</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45252</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>45252</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45252</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45253</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>45253</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45253</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45257</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45257</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45257</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>45258</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45258</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45259</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>45259</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45261</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>45265</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>45265</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45265</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45275</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>45275</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>45275</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>45275</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45279</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45279</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45279</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45279</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45279</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45281</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45281</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45281</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45281</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45282</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45282</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45282</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>45296</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>45301</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45301</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45301</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49785,7 +49785,7 @@
         <v>45307</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45308</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45308</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45310</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45312</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45314</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45316</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45320</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45330</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45338</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>45338</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50405,14 +50405,14 @@
     <row r="803" ht="15" customHeight="1">
       <c r="A803" t="inlineStr">
         <is>
-          <t>A 7065-2024</t>
+          <t>A 7048-2024</t>
         </is>
       </c>
       <c r="B803" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         </is>
       </c>
       <c r="G803" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="H803" t="n">
         <v>0</v>
@@ -50462,14 +50462,14 @@
     <row r="804" ht="15" customHeight="1">
       <c r="A804" t="inlineStr">
         <is>
-          <t>A 7048-2024</t>
+          <t>A 7065-2024</t>
         </is>
       </c>
       <c r="B804" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         </is>
       </c>
       <c r="G804" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="H804" t="n">
         <v>0</v>
@@ -50526,7 +50526,7 @@
         <v>45344</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -569,7 +569,7 @@
         <v>44970</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>45105</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45181</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>43627</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>44215</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>44651</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>44995</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45184</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>44980</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44977</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45252</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>43381</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44950</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44970</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45040</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45236</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45345</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>44361</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>44552</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44958</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45176</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45180</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>43768</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>44550</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>44551</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44662</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44875</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>44966</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44970</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>44984</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>43488</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>43549</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>43664</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43777</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44468</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44636</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44651</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44846</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>44887</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44950</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45009</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45105</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45142</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>45204</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45209</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45257</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>45294</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>43403</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>43486</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43635</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>43651</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>43847</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>43850</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>43860</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>43906</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43930</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43931</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44218</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44551</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44560</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>44595</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>44607</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44788</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44823</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44845</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44894</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>44911</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44960</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>45005</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45160</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45163</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45173</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45173</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45183</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>45208</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45212</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45253</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45310</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>45310</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45335</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>43336</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>43336</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>43343</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>43355</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43367</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>43371</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43378</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43385</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43412</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43416</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>43419</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43434</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43439</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43440</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>43446</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>43446</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>43446</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43447</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>43447</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>43450</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43450</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43451</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>43462</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43475</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43476</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43486</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>43488</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>43495</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>43496</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>43500</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>43517</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>43522</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>43528</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>43529</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>43539</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>43567</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>43606</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>43606</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>43612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>43612</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43642</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>43651</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43656</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>43656</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43668</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43676</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>43686</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>43692</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>43692</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>43706</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>43707</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>43711</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43733</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43733</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43734</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>43738</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>43740</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>43741</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>43746</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43747</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43756</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>43761</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>43770</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43770</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>43774</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43780</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>43780</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>43780</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>43795</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>43796</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>43797</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>43797</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>43801</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>43801</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>43802</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>43809</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>43809</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>43812</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>43829</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43839</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43843</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43853</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43853</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43859</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43859</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>43874</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>43875</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>43878</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>43880</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43882</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>43893</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>43896</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>43900</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>43906</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>43913</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>43913</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43938</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>43958</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>43964</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43965</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43983</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43985</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43985</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43985</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43993</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>44008</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>44013</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44021</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44022</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>44025</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>44029</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44043</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44049</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44056</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44056</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44056</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>44085</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44088</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44097</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>44106</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44111</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44116</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44123</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44144</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44150</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44151</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44154</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44154</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44164</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44165</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44166</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>44172</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44172</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44200</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>44208</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44208</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44211</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44214</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44215</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44218</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44231</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44237</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44266</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>44266</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>44270</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>44272</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44281</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44285</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44286</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>44286</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>44290</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>44291</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44308</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44309</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>44323</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>44333</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>44335</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44335</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44337</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44337</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44337</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44347</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44357</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44358</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44358</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44365</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44368</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44371</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44376</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44382</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44389</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>44389</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>44417</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44418</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44421</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44421</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44431</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>44434</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>44438</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>44439</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44439</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44439</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44446</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>44452</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>44452</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>44452</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>44452</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>44453</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>44453</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>44453</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44459</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44459</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44463</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44469</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44469</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44469</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44474</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44480</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44480</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44481</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44482</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44491</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44491</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44496</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44496</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44497</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44504</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44515</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44516</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44518</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44529</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>44532</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44543</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>44547</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>44548</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>44560</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>44571</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44578</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>44579</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44579</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>44580</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>44581</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44581</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>44581</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44588</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>44592</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>44594</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>44594</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44594</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44597</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44600</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>44603</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44616</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>44617</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>44620</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>44627</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>44627</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>44627</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>44627</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>44631</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>44631</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>44634</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>44636</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>44636</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>44638</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>44641</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>44644</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>44648</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>44648</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>44656</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44670</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>44672</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>44677</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>44677</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44684</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44684</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>44686</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>44687</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44689</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>44696</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>44698</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>44700</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44701</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>44701</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>44701</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>44704</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>44704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44704</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44705</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44708</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>44708</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44713</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>44713</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44715</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>44722</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>44725</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44726</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>44728</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>44732</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44734</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44734</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44735</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44739</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44739</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44742</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44743</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44743</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44748</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44749</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44749</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44750</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44750</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44755</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44756</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44756</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44769</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44769</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>44778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>44778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>44778</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44781</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44781</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44788</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44790</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44792</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44804</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44811</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44819</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>44819</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44824</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>44827</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>44837</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>44837</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>44841</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>44841</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>44843</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>44845</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44846</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44847</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44853</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>44853</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44853</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44858</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44858</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44858</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>44859</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>44859</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>44861</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44865</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44868</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44871</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44874</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44880</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44880</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44880</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44881</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44883</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44886</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44887</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44887</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44887</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44888</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44890</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44892</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44894</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44894</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44894</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>44894</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>44896</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>44896</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44900</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>44900</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>44901</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>44902</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44903</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>44906</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>44906</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>44907</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>44907</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>44908</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44909</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44909</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44911</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44916</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>44916</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44917</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44917</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44917</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>44922</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>44924</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>44924</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>44928</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>44929</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>44936</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>44937</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44939</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44942</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44944</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44945</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44945</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>44945</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44950</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44950</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44953</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>44953</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44956</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44956</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44956</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44959</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44964</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44964</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44964</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>44964</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>44964</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44964</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44964</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44964</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>44964</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44964</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44965</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         <v>44965</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>44966</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>44966</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>44966</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>44971</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44971</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44972</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44973</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44978</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44978</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44978</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44978</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>44979</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>44980</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>44980</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44980</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>44981</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>44984</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>44986</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44986</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44986</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44988</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>44991</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>44991</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44994</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45005</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45005</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45005</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45005</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45005</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45005</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45005</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45005</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45006</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45009</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45009</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45013</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45013</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45020</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45021</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45022</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45022</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45027</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45027</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45028</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45029</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45030</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45030</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45033</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45040</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>45040</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>45040</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45040</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45040</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45041</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45043</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>45046</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45046</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>45046</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45048</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45048</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45049</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45051</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45055</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>45057</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45057</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45057</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45058</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>45058</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>45058</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45061</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45061</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45062</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45063</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45063</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45070</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>45071</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45072</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45075</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45075</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45079</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45080</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45090</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45091</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45092</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45092</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45092</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45096</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>45096</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45096</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45098</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45099</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45103</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>45104</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45104</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>45105</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45105</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>45105</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45105</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45105</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>45105</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45105</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45106</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>45114</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>45114</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>45119</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45121</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45128</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45128</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45130</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45133</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45135</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>45135</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45135</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45138</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45146</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45153</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45161</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45161</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45162</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45162</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45163</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45163</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>45163</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45166</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>45166</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45167</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45168</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45170</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45170</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42512,7 +42512,7 @@
         <v>45173</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45173</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45173</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45174</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>45174</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45174</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>45176</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45176</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45180</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45181</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45181</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>45182</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45182</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45187</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45188</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45189</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45189</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45190</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45190</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45190</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45190</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>45190</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>45191</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45191</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45194</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>45197</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>45198</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45201</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>45203</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45203</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45204</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>45204</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45204</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45209</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45209</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45217</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45217</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45218</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45222</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45222</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45223</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45223</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45224</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>45226</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45226</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>45229</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45229</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45230</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45232</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45233</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45237</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45238</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45239</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45239</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>45239</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45239</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46491,7 +46491,7 @@
         <v>45242</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45243</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>45243</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45244</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45244</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45244</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45245</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45245</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45245</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45246</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>45246</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>45246</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45247</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45247</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>45247</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45247</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45247</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45247</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45251</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45252</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>45252</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45252</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45253</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>45253</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45253</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45257</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45257</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45257</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>45258</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45258</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45259</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>45259</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45261</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>45265</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>45265</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45265</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45275</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>45275</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>45275</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>45275</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45279</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45279</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45279</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45279</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45279</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45281</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45281</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45281</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45281</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45282</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45282</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45282</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>45296</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>45301</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45301</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45301</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49785,7 +49785,7 @@
         <v>45307</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45308</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45308</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45310</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45312</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45314</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45316</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45320</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45330</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50291,14 +50291,14 @@
     <row r="801" ht="15" customHeight="1">
       <c r="A801" t="inlineStr">
         <is>
-          <t>A 6395-2024</t>
+          <t>A 6385-2024</t>
         </is>
       </c>
       <c r="B801" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         </is>
       </c>
       <c r="G801" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="H801" t="n">
         <v>0</v>
@@ -50348,14 +50348,14 @@
     <row r="802" ht="15" customHeight="1">
       <c r="A802" t="inlineStr">
         <is>
-          <t>A 6385-2024</t>
+          <t>A 6395-2024</t>
         </is>
       </c>
       <c r="B802" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50368,7 +50368,7 @@
         </is>
       </c>
       <c r="G802" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="H802" t="n">
         <v>0</v>
@@ -50405,14 +50405,14 @@
     <row r="803" ht="15" customHeight="1">
       <c r="A803" t="inlineStr">
         <is>
-          <t>A 7048-2024</t>
+          <t>A 7065-2024</t>
         </is>
       </c>
       <c r="B803" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         </is>
       </c>
       <c r="G803" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="H803" t="n">
         <v>0</v>
@@ -50462,14 +50462,14 @@
     <row r="804" ht="15" customHeight="1">
       <c r="A804" t="inlineStr">
         <is>
-          <t>A 7065-2024</t>
+          <t>A 7048-2024</t>
         </is>
       </c>
       <c r="B804" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         </is>
       </c>
       <c r="G804" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="H804" t="n">
         <v>0</v>
@@ -50526,7 +50526,7 @@
         <v>45344</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -569,7 +569,7 @@
         <v>44970</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>45105</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45181</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>43627</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>44215</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>44651</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>44995</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45184</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>44980</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44977</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45252</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>43381</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44950</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44970</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45040</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45236</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45345</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>44361</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>44552</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44958</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45176</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45180</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>43768</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>44550</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>44551</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44662</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44875</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>44966</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44970</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>44984</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>43488</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>43549</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>43664</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43777</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44468</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44636</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44651</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44846</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>44887</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44950</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45009</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45105</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45142</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>45204</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45209</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45257</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>45294</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>43403</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>43486</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43635</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>43651</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>43847</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>43850</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>43860</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>43906</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43930</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43931</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44218</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44551</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44560</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>44595</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>44607</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44788</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44823</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44845</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44894</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>44911</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44960</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>45005</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45160</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45163</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45173</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45173</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45183</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>45208</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45212</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45253</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45310</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>45310</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45335</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>43336</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>43336</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>43343</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>43355</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43367</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>43371</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43378</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43385</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43412</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43416</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>43419</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43434</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43439</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43440</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>43446</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>43446</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>43446</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43447</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>43447</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>43450</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43450</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43451</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>43462</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43475</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43476</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43486</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>43488</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>43495</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>43496</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>43500</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>43517</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>43522</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>43528</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>43529</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>43539</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>43567</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>43606</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>43606</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>43612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>43612</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43642</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>43651</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43656</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>43656</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43668</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43676</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>43686</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>43692</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>43692</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>43706</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>43707</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>43711</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43733</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43733</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43734</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>43738</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>43740</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>43741</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>43746</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43747</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43756</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>43761</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>43770</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43770</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>43774</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43780</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>43780</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>43780</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>43795</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>43796</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>43797</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>43797</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>43801</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>43801</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>43802</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>43809</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>43809</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>43812</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>43829</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43839</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43843</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43853</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43853</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43859</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43859</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>43874</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>43875</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>43878</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>43880</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43882</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>43893</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>43896</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>43900</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>43906</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>43913</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>43913</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43938</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>43958</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>43964</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43965</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43983</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43985</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43985</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43985</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43993</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>44008</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>44013</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44021</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44022</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>44025</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>44029</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44043</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44049</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44056</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44056</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44056</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>44085</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44088</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44097</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>44106</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44111</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44116</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44123</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44144</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44150</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44151</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44154</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44154</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44164</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44165</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44166</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>44172</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44172</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44200</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>44208</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44208</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44211</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44214</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44215</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44218</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44231</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44237</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44266</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>44266</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>44270</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>44272</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44281</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44285</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44286</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>44286</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>44290</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>44291</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44308</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44309</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>44323</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>44333</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>44335</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44335</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44337</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44337</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44337</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44347</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44357</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44358</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44358</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44365</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44368</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44371</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44376</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44382</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44389</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>44389</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>44417</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44418</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44421</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44421</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44431</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>44434</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>44438</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>44439</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44439</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44439</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44446</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>44452</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>44452</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>44452</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>44452</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>44453</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>44453</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>44453</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44459</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44459</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44463</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44469</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44469</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44469</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44474</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44480</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44480</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44481</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44482</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44491</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44491</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44496</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44496</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44497</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44504</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44515</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44516</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44518</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44529</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>44532</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44543</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>44547</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>44548</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>44560</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>44571</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44578</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>44579</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44579</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>44580</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>44581</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44581</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>44581</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44588</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>44592</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>44594</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>44594</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44594</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44597</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44600</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>44603</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44616</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>44617</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>44620</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>44627</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>44627</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>44627</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>44627</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>44631</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>44631</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>44634</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>44636</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>44636</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>44638</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>44641</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>44644</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>44648</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>44648</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>44656</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44670</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>44672</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>44677</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>44677</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44684</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44684</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>44686</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>44687</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44689</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>44696</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>44698</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>44700</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44701</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>44701</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>44701</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>44704</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>44704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44704</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44705</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44708</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>44708</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44713</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>44713</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44715</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>44722</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>44725</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44726</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>44728</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>44732</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44734</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44734</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44735</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44739</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44739</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44742</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44743</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44743</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44748</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44749</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44749</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44750</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44750</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44755</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44756</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44756</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44769</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44769</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>44778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>44778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>44778</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44781</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44781</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44788</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44790</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44792</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44804</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44811</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44819</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>44819</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44824</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>44827</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>44837</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>44837</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>44841</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>44841</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>44843</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>44845</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44846</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44847</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44853</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>44853</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44853</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44858</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44858</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44858</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>44859</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>44859</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>44861</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44865</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44868</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44871</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44874</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44880</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44880</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44880</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44881</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44883</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44886</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44887</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44887</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44887</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44888</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44890</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44892</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44894</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44894</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44894</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>44894</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>44896</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>44896</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44900</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>44900</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>44901</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>44902</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44903</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>44906</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>44906</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>44907</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>44907</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>44908</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44909</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44909</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44911</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44916</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>44916</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44917</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44917</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44917</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>44922</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>44924</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>44924</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>44928</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>44929</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>44936</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>44937</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44939</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44942</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44944</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44945</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44945</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>44945</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44950</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44950</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44953</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>44953</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44956</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44956</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44956</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44959</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44964</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44964</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44964</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>44964</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>44964</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44964</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44964</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44964</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>44964</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44964</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44965</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         <v>44965</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>44966</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>44966</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>44966</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>44971</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44971</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44972</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44973</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44978</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44978</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44978</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44978</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>44979</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>44980</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>44980</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44980</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>44981</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>44984</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>44986</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44986</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44986</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44988</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>44991</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>44991</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44994</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45005</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45005</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45005</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45005</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45005</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45005</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45005</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45005</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45006</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45009</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45009</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45013</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45013</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45020</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45021</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45022</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45022</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45027</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45027</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45028</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45029</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45030</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45030</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45033</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45040</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>45040</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>45040</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45040</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45040</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45041</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45043</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>45046</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45046</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>45046</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45048</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45048</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45049</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45051</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45055</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>45057</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45057</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45057</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45058</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>45058</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>45058</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45061</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45061</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45062</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45063</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45063</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45070</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>45071</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45072</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45075</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45075</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45079</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45080</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45090</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45091</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45092</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45092</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45092</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45096</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>45096</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45096</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45098</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45099</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45103</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>45104</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45104</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>45105</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45105</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>45105</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45105</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45105</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>45105</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45105</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45106</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>45114</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>45114</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>45119</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45121</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45128</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45128</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45130</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45133</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45135</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>45135</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45135</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45138</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45146</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45153</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45161</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45161</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45162</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45162</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45163</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45163</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>45163</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45166</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>45166</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45167</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45168</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45170</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45170</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42512,7 +42512,7 @@
         <v>45173</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45173</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45173</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45174</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>45174</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45174</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>45176</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45176</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45180</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45181</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45181</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>45182</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45182</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45187</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45188</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45189</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45189</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45190</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45190</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45190</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45190</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>45190</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>45191</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45191</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45194</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>45197</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>45198</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45201</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>45203</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45203</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45204</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>45204</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45204</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45209</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45209</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45217</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45217</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45218</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45222</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45222</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45223</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45223</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45224</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>45226</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45226</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>45229</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45229</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45230</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45232</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45233</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45237</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45238</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45239</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45239</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>45239</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45239</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46491,7 +46491,7 @@
         <v>45242</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45243</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>45243</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45244</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45244</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45244</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45245</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45245</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45245</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45246</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>45246</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>45246</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45247</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45247</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>45247</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45247</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45247</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45247</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45251</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45252</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>45252</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45252</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45253</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>45253</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45253</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45257</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45257</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45257</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>45258</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45258</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45259</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>45259</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45261</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>45265</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>45265</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45265</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45275</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>45275</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>45275</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>45275</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45279</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45279</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45279</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45279</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45279</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45281</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45281</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45281</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45281</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45282</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45282</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45282</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>45296</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>45301</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45301</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45301</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49785,7 +49785,7 @@
         <v>45307</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45308</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45308</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45310</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45312</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45314</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45316</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45320</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45330</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45338</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>45338</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50405,14 +50405,14 @@
     <row r="803" ht="15" customHeight="1">
       <c r="A803" t="inlineStr">
         <is>
-          <t>A 7065-2024</t>
+          <t>A 7048-2024</t>
         </is>
       </c>
       <c r="B803" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         </is>
       </c>
       <c r="G803" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="H803" t="n">
         <v>0</v>
@@ -50462,14 +50462,14 @@
     <row r="804" ht="15" customHeight="1">
       <c r="A804" t="inlineStr">
         <is>
-          <t>A 7048-2024</t>
+          <t>A 7065-2024</t>
         </is>
       </c>
       <c r="B804" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         </is>
       </c>
       <c r="G804" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="H804" t="n">
         <v>0</v>
@@ -50526,7 +50526,7 @@
         <v>45344</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -569,7 +569,7 @@
         <v>44970</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>45105</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45181</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>43627</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>44215</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>44651</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>44995</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45184</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>44980</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44977</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45252</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>43381</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44950</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44970</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45040</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45236</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45345</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>44361</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>44552</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44958</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45176</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45180</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>43768</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>44550</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>44551</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44662</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44875</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>44966</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44970</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>44984</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>43488</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>43549</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>43664</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43777</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44468</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44636</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44651</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44846</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>44887</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44950</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45009</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45105</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45142</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>45204</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45209</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45257</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>45294</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>43403</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>43486</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43635</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>43651</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>43847</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>43850</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>43860</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>43906</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43930</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43931</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44218</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44551</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44560</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>44595</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>44607</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44788</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44823</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44845</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44894</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>44911</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44960</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>45005</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45160</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45163</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45173</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45173</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45183</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>45208</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45212</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45253</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45310</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>45310</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45335</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>43336</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>43336</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>43343</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>43355</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43367</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>43371</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43378</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43385</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43412</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43416</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>43419</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43434</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43439</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43440</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>43446</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>43446</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>43446</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43447</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>43447</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>43450</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43450</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43451</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>43462</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43475</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43476</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43486</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>43488</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>43495</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>43496</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>43500</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>43517</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>43522</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>43528</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>43529</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>43539</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>43567</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>43606</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>43606</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>43612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>43612</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43642</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>43651</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43656</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>43656</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43668</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43676</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>43686</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>43692</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>43692</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>43706</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>43707</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>43711</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43733</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43733</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43734</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>43738</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>43740</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>43741</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>43746</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43747</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43756</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>43761</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>43770</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43770</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>43774</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43780</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>43780</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>43780</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>43795</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>43796</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>43797</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>43797</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>43801</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>43801</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>43802</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>43809</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>43809</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>43812</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>43829</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43839</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43843</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43853</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43853</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43859</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43859</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>43874</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>43875</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>43878</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>43880</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43882</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>43893</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>43896</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>43900</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>43906</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>43913</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>43913</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43938</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>43958</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>43964</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43965</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43983</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43985</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43985</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43985</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43993</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>44008</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>44013</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44021</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44022</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>44025</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>44029</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44043</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44049</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44056</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44056</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44056</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>44085</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44088</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44097</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>44106</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44111</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44116</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44123</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44144</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44150</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44151</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44154</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44154</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44164</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44165</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44166</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>44172</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44172</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44200</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>44208</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44208</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44211</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44214</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44215</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44218</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44231</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44237</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44266</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>44266</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>44270</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>44272</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44281</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44285</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44286</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>44286</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>44290</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>44291</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44308</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44309</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>44323</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>44333</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>44335</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44335</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44337</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44337</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44337</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44347</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44357</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44358</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44358</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44365</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44368</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44371</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44376</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44382</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44389</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>44389</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>44417</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44418</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44421</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44421</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44431</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>44434</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>44438</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>44439</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44439</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44439</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44446</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>44452</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>44452</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>44452</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>44452</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>44453</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>44453</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>44453</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44459</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44459</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44463</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44469</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44469</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44469</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44474</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44480</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44480</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44481</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44482</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44491</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44491</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44496</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44496</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44497</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44504</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44515</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44516</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44518</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44529</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>44532</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44543</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>44547</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>44548</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>44560</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>44571</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44578</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>44579</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44579</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>44580</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>44581</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44581</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>44581</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44588</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>44592</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>44594</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>44594</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44594</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44597</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44600</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>44603</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44616</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>44617</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>44620</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>44627</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>44627</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>44627</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>44627</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>44631</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>44631</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>44634</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>44636</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>44636</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>44638</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>44641</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>44644</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>44648</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>44648</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>44656</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44670</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>44672</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>44677</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>44677</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44684</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44684</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>44686</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>44687</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44689</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>44696</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>44698</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>44700</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44701</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>44701</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>44701</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>44704</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>44704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44704</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44705</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44708</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>44708</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44713</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>44713</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44715</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>44722</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>44725</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44726</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>44728</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>44732</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44734</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44734</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44735</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44739</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44739</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44742</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44743</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44743</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44748</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44749</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44749</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44750</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44750</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44755</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44756</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44756</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44769</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44769</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>44778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>44778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>44778</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44781</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44781</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44788</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44790</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44792</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44804</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44811</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44819</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>44819</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44824</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>44827</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>44837</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>44837</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>44841</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>44841</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>44843</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>44845</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44846</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44847</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44853</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>44853</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44853</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44858</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44858</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44858</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>44859</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>44859</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>44861</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44865</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44868</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44871</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44874</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44880</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44880</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44880</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44881</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44883</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44886</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44887</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44887</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44887</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44888</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44890</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44892</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44894</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44894</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44894</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>44894</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>44896</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>44896</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44900</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>44900</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>44901</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>44902</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44903</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>44906</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>44906</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>44907</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>44907</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>44908</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44909</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44909</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44911</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44916</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>44916</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44917</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44917</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44917</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>44922</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>44924</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>44924</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>44928</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>44929</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>44936</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>44937</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44939</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44942</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44944</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44945</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44945</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>44945</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44950</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44950</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44953</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>44953</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44956</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44956</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44956</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44959</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44964</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44964</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44964</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>44964</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>44964</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44964</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44964</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44964</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>44964</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44964</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44965</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         <v>44965</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>44966</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>44966</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>44966</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>44971</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44971</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44972</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44973</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44978</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44978</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44978</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44978</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>44979</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>44980</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>44980</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44980</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>44981</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>44984</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>44986</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44986</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44986</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44988</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>44991</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>44991</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44994</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45005</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45005</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45005</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45005</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45005</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45005</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45005</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45005</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45006</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45009</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45009</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45013</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45013</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45020</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45021</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45022</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45022</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45027</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45027</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45028</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45029</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45030</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45030</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45033</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45040</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>45040</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>45040</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45040</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45040</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45041</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45043</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>45046</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45046</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>45046</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45048</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45048</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45049</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45051</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45055</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>45057</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45057</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45057</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45058</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>45058</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>45058</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45061</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45061</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38632,7 +38632,7 @@
         <v>45062</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45063</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38751,7 +38751,7 @@
         <v>45063</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38813,7 +38813,7 @@
         <v>45070</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38870,7 +38870,7 @@
         <v>45071</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45072</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38984,7 +38984,7 @@
         <v>45075</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>45075</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39108,7 +39108,7 @@
         <v>45079</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>45080</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39227,7 +39227,7 @@
         <v>45090</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45091</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45092</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>45092</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45092</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45096</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>45096</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39641,7 +39641,7 @@
         <v>45096</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45098</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39765,7 +39765,7 @@
         <v>45099</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45103</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>45104</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39946,7 +39946,7 @@
         <v>45104</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>45105</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45105</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>45105</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45105</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45105</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>45105</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45105</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45106</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40464,7 +40464,7 @@
         <v>45114</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>45114</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>45119</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45121</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45127</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40754,7 +40754,7 @@
         <v>45128</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>45128</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45130</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45133</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45135</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41079,7 +41079,7 @@
         <v>45135</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45135</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>45138</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>45146</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>45153</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45161</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45161</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45161</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>45161</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45162</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45162</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45163</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45163</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>45163</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45166</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>45166</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42098,7 +42098,7 @@
         <v>45166</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>45166</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45166</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42269,7 +42269,7 @@
         <v>45167</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45168</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45170</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42450,7 +42450,7 @@
         <v>45170</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42512,7 +42512,7 @@
         <v>45173</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42574,7 +42574,7 @@
         <v>45173</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45173</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45174</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>45174</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45174</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>45176</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45176</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45180</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43055,7 +43055,7 @@
         <v>45181</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43112,7 +43112,7 @@
         <v>45181</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43169,7 +43169,7 @@
         <v>45182</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43231,7 +43231,7 @@
         <v>45182</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45187</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45188</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45189</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45189</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45190</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45190</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45190</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45190</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43769,7 +43769,7 @@
         <v>45190</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>45191</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45191</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45194</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>45197</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44069,7 +44069,7 @@
         <v>45198</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45201</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>45203</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45203</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45204</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>45204</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45204</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45209</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44550,7 +44550,7 @@
         <v>45209</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>45217</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44674,7 +44674,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44793,7 +44793,7 @@
         <v>45217</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45218</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45098,7 +45098,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45222</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45222</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45222</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45222</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45223</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>45223</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45224</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45730,7 +45730,7 @@
         <v>45226</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>45226</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>45229</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45229</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45230</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>45232</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45233</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45237</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>45238</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46258,7 +46258,7 @@
         <v>45239</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46315,7 +46315,7 @@
         <v>45239</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>45239</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46434,7 +46434,7 @@
         <v>45239</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46491,7 +46491,7 @@
         <v>45242</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45243</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>45243</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46667,7 +46667,7 @@
         <v>45244</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45244</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46781,7 +46781,7 @@
         <v>45244</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45245</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46900,7 +46900,7 @@
         <v>45245</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45245</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>45246</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>45246</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>45246</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47195,7 +47195,7 @@
         <v>45247</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45247</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>45247</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47366,7 +47366,7 @@
         <v>45247</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45247</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45247</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45251</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45252</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>45252</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47713,7 +47713,7 @@
         <v>45252</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45253</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>45253</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45253</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45257</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45257</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45257</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>45258</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>45258</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45259</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>45259</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45261</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48412,7 +48412,7 @@
         <v>45265</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>45265</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45265</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45275</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48640,7 +48640,7 @@
         <v>45275</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>45275</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48754,7 +48754,7 @@
         <v>45275</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48816,7 +48816,7 @@
         <v>45279</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45279</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48930,7 +48930,7 @@
         <v>45279</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48987,7 +48987,7 @@
         <v>45279</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49044,7 +49044,7 @@
         <v>45279</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49101,7 +49101,7 @@
         <v>45281</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>45281</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49215,7 +49215,7 @@
         <v>45281</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49272,7 +49272,7 @@
         <v>45281</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>45282</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45282</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>45282</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45296</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>45296</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49614,7 +49614,7 @@
         <v>45301</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45301</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45301</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49785,7 +49785,7 @@
         <v>45307</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45308</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45308</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45310</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45312</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45314</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45316</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>45320</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45330</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45338</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>45338</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50412,7 +50412,7 @@
         <v>45343</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50469,7 +50469,7 @@
         <v>45343</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50526,7 +50526,7 @@
         <v>45344</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>

--- a/Översikt TIERP.xlsx
+++ b/Översikt TIERP.xlsx
@@ -569,7 +569,7 @@
         <v>44970</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>45105</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45181</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>43627</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>44215</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>44651</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>44995</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>45184</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>44980</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44977</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>45252</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>43381</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44950</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44970</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45040</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45236</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45345</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>44361</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>44552</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>44958</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>45176</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>45180</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>43768</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>44550</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>44551</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>44662</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         <v>44875</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>44966</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>44970</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>44984</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>43488</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>43549</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>43664</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43777</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44468</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>44636</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44651</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>44846</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>44887</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44950</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>44956</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>45009</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45105</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45142</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>45204</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45209</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>45257</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>45294</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>43403</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>43486</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>43635</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>43651</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>43847</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>43850</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>43860</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>43906</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>43930</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>43931</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44218</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>44551</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44560</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>44595</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>44607</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44788</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44823</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44845</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>44894</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>44911</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>44960</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>45005</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45160</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>45163</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45173</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>45173</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45183</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7719,7 +7719,7 @@
         <v>45208</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45212</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>45253</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>45310</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>45310</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>45335</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>43336</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>43336</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>43343</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>43355</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>43367</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>43371</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>43378</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>43385</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>43412</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>43416</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>43419</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>43424</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>43427</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         <v>43434</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>43438</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>43439</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>43440</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>43446</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>43446</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>43446</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>43447</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>43447</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>43450</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>43450</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>43450</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>43451</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>43462</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>43475</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>43476</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>43486</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>43486</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>43488</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>43488</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>43488</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>43495</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>43496</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>43500</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>43514</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>43517</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>43521</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>43522</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>43528</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>43528</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>43529</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>43536</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>43539</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>43559</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>43567</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>43606</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>43606</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>43612</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>43612</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>43633</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>43641</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         <v>43642</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>43651</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>43656</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>43656</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>43668</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>43676</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>43686</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>43692</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>43692</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>43706</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>43707</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>43711</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>43733</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>43733</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>43734</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>43738</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>43740</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>43741</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>43746</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>43747</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>43756</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>43761</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>43770</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>43770</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>43774</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>43780</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>43780</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>43780</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>43795</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>43796</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>43797</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>43797</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>43801</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>43801</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>43802</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>43809</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>43809</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>43812</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>43829</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>43839</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>43843</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>43853</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>43853</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>43859</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>43859</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>43874</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>43875</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>43878</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>43880</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>43882</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>43893</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>43896</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>43900</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>43901</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>43906</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14802,7 +14802,7 @@
         <v>43913</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>43913</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>43930</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>43936</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>43938</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>43957</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>43958</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>43963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>43964</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43965</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43983</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>43985</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>43985</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>43985</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>43993</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44006</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>44007</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>44008</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>44013</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>44021</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15992,7 +15992,7 @@
         <v>44022</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>44025</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>44029</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44043</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44049</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>44056</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16344,7 +16344,7 @@
         <v>44056</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>44056</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>44085</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44088</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44097</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>44106</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44111</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44116</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44123</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44144</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44150</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44151</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44154</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44154</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44154</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44164</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>44165</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44166</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>44172</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44172</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44200</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>44208</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44208</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44211</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44214</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44215</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44218</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44231</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44237</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44266</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18146,7 +18146,7 @@
         <v>44266</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>44270</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>44272</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>44281</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>44285</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>44286</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>44286</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>44290</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>44291</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44308</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>44309</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>44323</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>44333</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>44335</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>44335</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>44337</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>44337</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44337</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>44347</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44357</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44358</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>44358</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>44365</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>44368</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>44371</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44376</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>44382</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>44389</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>44389</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>44417</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>44418</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>44421</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44421</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20147,7 +20147,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>44431</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20266,7 +20266,7 @@
         <v>44434</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>44438</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>44439</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>44439</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>44439</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44446</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>44452</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>44452</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>44452</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>44452</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>44453</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44453</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>44453</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>44453</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44459</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44459</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>44463</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44469</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>44469</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>44469</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44474</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44480</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44480</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44481</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44482</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44491</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44491</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>44496</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44496</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>44497</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44504</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44515</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22284,7 +22284,7 @@
         <v>44516</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>44518</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>44529</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>44532</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44543</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>44547</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>44548</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>44560</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>44571</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44578</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>44579</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22916,7 +22916,7 @@
         <v>44579</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>44580</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>44581</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>44581</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>44581</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44588</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>44592</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>44594</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>44594</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>44594</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44597</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>44600</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>44603</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>44616</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>44617</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>44620</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>44627</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>44627</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>44627</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24086,7 +24086,7 @@
         <v>44627</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24143,7 +24143,7 @@
         <v>44631</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>44631</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>44634</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>44636</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>44636</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>44638</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>44641</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>44644</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>44648</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>44648</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>44656</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44670</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>44672</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>44677</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24951,7 +24951,7 @@
         <v>44677</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44684</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>44684</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>44686</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>44687</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44689</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>44696</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>44698</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>44700</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>44701</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>44701</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>44701</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>44704</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>44704</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25769,7 +25769,7 @@
         <v>44704</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44704</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44705</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44708</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>44708</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26131,7 +26131,7 @@
         <v>44713</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>44713</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44715</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>44722</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>44725</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44726</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>44728</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>44732</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>44734</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44734</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>44735</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>44739</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>44739</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44742</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>44743</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>44743</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>44748</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>44749</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>44749</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>44750</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>44750</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>44755</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44756</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44756</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44756</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44769</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>44769</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>44778</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>44778</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27911,7 +27911,7 @@
         <v>44778</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         <v>44781</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28025,7 +28025,7 @@
         <v>44781</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>44788</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44790</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44792</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>44804</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>44811</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44819</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>44819</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44824</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>44827</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>44837</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>44837</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28771,7 +28771,7 @@
         <v>44841</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>44841</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>44843</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>44845</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>44846</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>44847</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>44853</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29175,7 +29175,7 @@
         <v>44853</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44853</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44858</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44858</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44858</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>44859</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>44859</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>44859</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>44861</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>44865</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44865</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>44865</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44868</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44871</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44874</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44880</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44880</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>44880</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>44881</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>44883</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44886</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30397,7 +30397,7 @@
         <v>44887</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44887</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44887</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44888</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44890</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44892</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44894</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>44894</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>44894</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>44894</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>44896</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>44896</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44900</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>44900</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31205,7 +31205,7 @@
         <v>44900</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>44901</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>44902</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44903</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>44906</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>44906</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>44907</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>44907</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>44908</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>44909</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         <v>44909</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31842,7 +31842,7 @@
         <v>44911</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44916</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>44916</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>44917</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44917</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44917</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>44922</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>44924</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>44924</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>44928</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>44929</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32479,7 +32479,7 @@
         <v>44936</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>44936</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>44937</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32650,7 +32650,7 @@
         <v>44939</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>44942</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44944</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>44945</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44945</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>44945</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32992,7 +32992,7 @@
         <v>44950</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33049,7 +33049,7 @@
         <v>44950</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>44953</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>44953</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44956</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33282,7 +33282,7 @@
         <v>44956</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>44956</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44956</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44959</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>44964</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33567,7 +33567,7 @@
         <v>44964</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>44964</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>44964</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>44964</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44964</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44964</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>44964</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>44964</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>44964</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>44964</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44965</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         <v>44965</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34301,7 +34301,7 @@
         <v>44966</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34363,7 +34363,7 @@
         <v>44966</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>44966</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>44971</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>44971</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34596,7 +34596,7 @@
         <v>44972</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>44973</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44978</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>44978</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34824,7 +34824,7 @@
         <v>44978</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34881,7 +34881,7 @@
         <v>44978</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34938,7 +34938,7 @@
         <v>44979</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>44980</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>44980</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
         <v>44980</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>44981</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>44984</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>44986</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35342,7 +35342,7 @@
         <v>44986</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>44986</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35456,7 +35456,7 @@
         <v>44988</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>44991</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>44991</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>44994</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>45005</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45005</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45005</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45005</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45005</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45005</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>45005</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45005</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45006</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45009</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45009</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45013</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45013</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45020</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45021</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45022</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45022</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>45022</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45027</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45027</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45028</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45029</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45030</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45030</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>45033</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45040</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>45040</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37328,7 +37328,7 @@
         <v>45040</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37390,7 +37390,7 @@
         <v>45040</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37452,7 +37452,7 @@
         <v>45040</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37509,7 +37509,7 @@
         <v>45040</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37571,7 +37571,7 @@
         <v>45041</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37633,7 +37633,7 @@
         <v>45043</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>45046</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37752,7 +37752,7 @@
         <v>45046</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37809,7 +37809,7 @@
         <v>45046</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45048</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37928,7 +37928,7 @@
         <v>45048</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37990,7 +37990,7 @@
         <v>45049</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45051</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>45055</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38161,7 +38161,7 @@
         <v>45057</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>45057</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45057</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>45058</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>45058</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38451,7 +38451,7 @@
         <v>45058</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>45061</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -3